--- a/excel/EX02_moisture_aw.xlsx
+++ b/excel/EX02_moisture_aw.xlsx
@@ -10834,17 +10834,17 @@
     <row r="9" ht="60" customHeight="1">
       <c r="B9" s="42" t="inlineStr"/>
     </row>
-    <row r="11" ht="32" customHeight="1">
+    <row r="11" ht="48" customHeight="1">
       <c r="B11" s="41" t="inlineStr">
         <is>
-          <t>問題 3：恆重判斷：連續三次乾燥後秤重 12.4050 g → 12.3890 g → 12.3860 g。第幾次秤重後才算恆重？該用哪一個重量算水分？</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
+          <t>問題 3：恆重判斷：連續三次乾燥後秤重 12.4050 g → 12.3890 g → 12.3860 g。(1) 第 3 次秤重後達到恆重了嗎？(2) 如果還沒，下一步該做什麼？(3) 再烘一次後第 4 次秤得 12.3851 g，現在恆重了嗎？該用哪一個重量算水分？</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
       <c r="B12" s="18" t="inlineStr">
         <is>
-          <t>提示：把「2_濕基乾基」C23–C25 改成這三個數字，看 C28 的判定。想一想：如果判定是「仍未恆重」，下一步該做什麼？</t>
+          <t>提示：把「2_濕基乾基」C23–C25 改成這三個數字，看 C28 的判定。第 (3) 小題：把 C23–C25 改成第 2、3、4 次的重量（12.3890、12.3860、12.3851）再看一次判定。</t>
         </is>
       </c>
     </row>

--- a/excel/EX02_moisture_aw.xlsx
+++ b/excel/EX02_moisture_aw.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="0_說明" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="1_原始數據" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="2_濕基乾基" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="3_烘箱法恆重" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="4_各組統計" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="5_烘箱vs紅外線" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="6_水活性" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="7_共同盲樣" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="練習題" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0_說明" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_原始數據" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_濕基乾基" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_烘箱法恆重" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_各組統計" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_烘箱vs紅外線" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_水活性" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_共同盲樣" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8_吸濕曲線" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="練習題" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,15 +25,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
+  <numFmts count="7">
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="+0.000;-0.000;0.000"/>
     <numFmt numFmtId="168" formatCode="+0.000;-0.000"/>
     <numFmt numFmtId="169" formatCode="0.0000E+00"/>
+    <numFmt numFmtId="170" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -77,6 +79,11 @@
       <color rgb="001E6B66"/>
       <sz val="11"/>
       <u val="single"/>
+    </font>
+    <font>
+      <name val="Microsoft JhengHei"/>
+      <color rgb="005B6964"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="6">
@@ -177,7 +184,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -195,17 +202,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -216,19 +223,19 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -245,7 +252,7 @@
     <xf numFmtId="168" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -258,7 +265,7 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -267,11 +274,81 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -283,6 +360,13 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00FFE699"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FCE4D6"/>
         </patternFill>
       </fill>
     </dxf>
@@ -360,14 +444,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -388,7 +472,7 @@
             <v>each student</v>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -397,10 +481,10 @@
             <symbol val="circle"/>
             <size val="7"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="4A6FA5"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:solidFill>
                   <a:srgbClr val="4A6FA5"/>
                 </a:solidFill>
@@ -427,7 +511,7 @@
             <v>mean bias</v>
           </tx>
           <spPr>
-            <a:ln w="19050">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
               <a:solidFill>
                 <a:srgbClr val="B3306A"/>
               </a:solidFill>
@@ -437,7 +521,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -461,7 +545,7 @@
             <v>zero</v>
           </tx>
           <spPr>
-            <a:ln w="19050">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
               <a:solidFill>
                 <a:srgbClr val="5B6964"/>
               </a:solidFill>
@@ -471,7 +555,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -503,8 +587,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -531,8 +615,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -561,14 +645,14 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -589,7 +673,7 @@
             <v>beef_jerky</v>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -598,10 +682,10 @@
             <symbol val="circle"/>
             <size val="7"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="B3306A"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:solidFill>
                   <a:srgbClr val="B3306A"/>
                 </a:solidFill>
@@ -628,7 +712,7 @@
             <v>dried_longan</v>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -637,10 +721,10 @@
             <symbol val="square"/>
             <size val="7"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="1E6B66"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:solidFill>
                   <a:srgbClr val="1E6B66"/>
                 </a:solidFill>
@@ -667,7 +751,7 @@
             <v>white_bread</v>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -676,10 +760,10 @@
             <symbol val="triangle"/>
             <size val="7"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="D08A1E"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:solidFill>
                   <a:srgbClr val="D08A1E"/>
                 </a:solidFill>
@@ -706,7 +790,7 @@
             <v>potato_chips</v>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -715,10 +799,10 @@
             <symbol val="diamond"/>
             <size val="7"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="4A6FA5"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:solidFill>
                   <a:srgbClr val="4A6FA5"/>
                 </a:solidFill>
@@ -745,7 +829,7 @@
             <v>milk_powder</v>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -754,10 +838,10 @@
             <symbol val="circle"/>
             <size val="7"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="7A5C99"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:solidFill>
                   <a:srgbClr val="7A5C99"/>
                 </a:solidFill>
@@ -784,7 +868,7 @@
             <v>honey</v>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -793,10 +877,10 @@
             <symbol val="square"/>
             <size val="7"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="6B8E23"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:solidFill>
                   <a:srgbClr val="6B8E23"/>
                 </a:solidFill>
@@ -823,7 +907,7 @@
             <v>bacteria min</v>
           </tx>
           <spPr>
-            <a:ln w="12700">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
               <a:solidFill>
                 <a:srgbClr val="6F7A76"/>
               </a:solidFill>
@@ -833,7 +917,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -857,7 +941,7 @@
             <v>yeast min</v>
           </tx>
           <spPr>
-            <a:ln w="12700">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
               <a:solidFill>
                 <a:srgbClr val="6F7A76"/>
               </a:solidFill>
@@ -867,7 +951,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -891,7 +975,7 @@
             <v>mold min</v>
           </tx>
           <spPr>
-            <a:ln w="12700">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
               <a:solidFill>
                 <a:srgbClr val="6F7A76"/>
               </a:solidFill>
@@ -901,7 +985,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -925,7 +1009,7 @@
             <v>xerophilic mold min</v>
           </tx>
           <spPr>
-            <a:ln w="12700">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
               <a:solidFill>
                 <a:srgbClr val="6F7A76"/>
               </a:solidFill>
@@ -935,7 +1019,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -967,8 +1051,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -999,8 +1083,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1029,8 +1113,545 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Noodle isotherm (28 °C) with GAB curve from ⑤</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <scatterChart>
+        <scatterStyle val="lineMarker"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Oven</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="7"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="1E6B66"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="1E6B66"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'8_吸濕曲線'!$B$5:$B$12</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'8_吸濕曲線'!$E$5:$E$12</f>
+            </numRef>
+          </yVal>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>FD-660 (IR)</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="square"/>
+            <size val="7"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="D08A1E"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="D08A1E"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'8_吸濕曲線'!$B$5:$B$12</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'8_吸濕曲線'!$F$5:$F$12</f>
+            </numRef>
+          </yVal>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>GAB (⑤ parameters)</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="B3306A"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'8_吸濕曲線'!$S$5:$S$23</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'8_吸濕曲線'!$T$5:$T$23</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="20"/>
+      </scatterChart>
+      <valAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="1"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>aw</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="0.0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <crossAx val="20"/>
+      </valAx>
+      <valAx>
+        <axId val="20"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="0.3"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>X (g water / g dry matter)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="0.00" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>BET linearisation: all points lie outside aw 0.05-0.45</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <scatterChart>
+        <scatterStyle val="lineMarker"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>data</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="7"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="4A6FA5"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="4A6FA5"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <trendline>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="B3306A"/>
+                </a:solidFill>
+                <a:prstDash val="dash"/>
+              </a:ln>
+            </spPr>
+            <trendlineType val="linear"/>
+            <forward val="0.08"/>
+            <backward val="0.5580000000000001"/>
+            <dispRSqr val="1"/>
+            <dispEq val="0"/>
+          </trendline>
+          <xVal>
+            <numRef>
+              <f>'8_吸濕曲線'!$B$5:$B$12</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'8_吸濕曲線'!$H$5:$H$12</f>
+            </numRef>
+          </yVal>
+        </ser>
+        <axId val="10"/>
+        <axId val="20"/>
+      </scatterChart>
+      <valAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="1"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>aw</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="0.0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <crossAx val="20"/>
+      </valAx>
+      <valAx>
+        <axId val="20"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="40"/>
+          <min val="-35"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>aw / [(1 - aw) X]</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Profile of Xm: Delta below 3.84 = data cannot tell</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <scatterChart>
+        <scatterStyle val="lineMarker"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Delta</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="1E6B66"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'8_吸濕曲線'!$A$20:$A$68</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'8_吸濕曲線'!$F$20:$F$68</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>3.84 (95%)</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="D08A1E"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'8_吸濕曲線'!$S$27:$S$28</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'8_吸濕曲線'!$T$27:$T$28</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="20"/>
+      </scatterChart>
+      <valAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="0.15"/>
+          <min val="0.03"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Fixed Xm (g/g)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="0.00" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <crossAx val="20"/>
+      </valAx>
+      <valAx>
+        <axId val="20"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="20"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Delta</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>EX02</author>
+  </authors>
+  <commentList>
+    <comment ref="B20" authorId="0" shapeId="0">
+      <text>
+        <t>C 撞到上限 1000：Xm 太小時，GAB 無論如何都配不上數據，C 被推到邊界。</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -1045,9 +1666,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1057,7 +1678,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>5</col>
@@ -1072,9 +1693,80 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>71</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="3060000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>71</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="3060000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>89</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="3060000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1446,6 +2138,13 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>•  （延伸）用真實麵條數據畫等溫吸濕曲線，判斷 BET／GAB 算出的單分子層水 Xm 撐不撐得住（「8_吸濕曲線」）。</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
       <c r="B12" s="3" t="inlineStr">
         <is>
@@ -1575,11 +2274,11 @@
           <t>G1_S1 牛肉乾 濕基水分 (%)</t>
         </is>
       </c>
-      <c r="C29" s="11">
+      <c r="C29" s="43">
         <f>'3_烘箱法恆重'!Q5</f>
         <v/>
       </c>
-      <c r="D29" s="12" t="n">
+      <c r="D29" s="44" t="n">
         <v>20.42062415196735</v>
       </c>
       <c r="E29" s="13">
@@ -1593,11 +2292,11 @@
           <t>G1_S1 牛肉乾 乾基水分 (%)</t>
         </is>
       </c>
-      <c r="C30" s="11">
+      <c r="C30" s="43">
         <f>'3_烘箱法恆重'!R5</f>
         <v/>
       </c>
-      <c r="D30" s="12" t="n">
+      <c r="D30" s="44" t="n">
         <v>25.66069906223345</v>
       </c>
       <c r="E30" s="13">
@@ -1611,11 +2310,11 @@
           <t>G3_S2 白吐司 濕基水分（用第 3 次秤重）(%)</t>
         </is>
       </c>
-      <c r="C31" s="11">
+      <c r="C31" s="43">
         <f>'3_烘箱法恆重'!Q12</f>
         <v/>
       </c>
-      <c r="D31" s="12" t="n">
+      <c r="D31" s="44" t="n">
         <v>35.28132107188775</v>
       </c>
       <c r="E31" s="13">
@@ -1629,11 +2328,11 @@
           <t>白吐司（第 3 組）RSD (%)</t>
         </is>
       </c>
-      <c r="C32" s="11">
+      <c r="C32" s="43">
         <f>'4_各組統計'!F7</f>
         <v/>
       </c>
-      <c r="D32" s="12" t="n">
+      <c r="D32" s="44" t="n">
         <v>1.521855236270101</v>
       </c>
       <c r="E32" s="13">
@@ -1647,11 +2346,11 @@
           <t>洋芋片（第 4 組）RSD (%)</t>
         </is>
       </c>
-      <c r="C33" s="11">
+      <c r="C33" s="43">
         <f>'4_各組統計'!F8</f>
         <v/>
       </c>
-      <c r="D33" s="12" t="n">
+      <c r="D33" s="44" t="n">
         <v>25.83607439894361</v>
       </c>
       <c r="E33" s="13">
@@ -1665,11 +2364,11 @@
           <t>平均偏差 IR − 烘箱 (%)</t>
         </is>
       </c>
-      <c r="C34" s="11">
+      <c r="C34" s="43">
         <f>'5_烘箱vs紅外線'!J6</f>
         <v/>
       </c>
-      <c r="D34" s="12" t="n">
+      <c r="D34" s="44" t="n">
         <v>-0.4986190314390423</v>
       </c>
       <c r="E34" s="13">
@@ -1683,11 +2382,11 @@
           <t>成對 t 值</t>
         </is>
       </c>
-      <c r="C35" s="14">
+      <c r="C35" s="45">
         <f>'5_烘箱vs紅外線'!J9</f>
         <v/>
       </c>
-      <c r="D35" s="15" t="n">
+      <c r="D35" s="46" t="n">
         <v>-8.644386893055584</v>
       </c>
       <c r="E35" s="13">
@@ -1763,6 +2462,18 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="B43" s="19" t="inlineStr">
+        <is>
+          <t>延伸：麵條等溫吸濕曲線（互動網頁）</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>https://tai-shengyeh.github.io/food-analysis-lab/labs/w02_moisture/isotherm.html</t>
+        </is>
+      </c>
+    </row>
     <row r="44">
       <c r="B44" s="3" t="inlineStr">
         <is>
@@ -1799,7 +2510,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="20">
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="B24:E24"/>
@@ -1814,6 +2525,7 @@
     <mergeCell ref="B18:E18"/>
     <mergeCell ref="B21:E21"/>
     <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B11:E11"/>
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="B19:E19"/>
@@ -1825,6 +2537,153 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" r:id="rId3"/>
   </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00B3306A"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:B30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>練習題（寫在黃色格子裡，交報告時一起附上）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="48" customHeight="1">
+      <c r="B3" s="41" t="inlineStr">
+        <is>
+          <t>問題 1：牛肉乾質量平衡：工廠影片聲稱「500 g 鮮肉 → 100 g 牛肉乾」。瘦牛肉約 73% 水分，成品約 20% 水分，加工中固形物幾乎不流失。(1) 用質量平衡算合理的產率 (%) 與成品克數；(2) 跟影片的 100 g 差多少？(3) 若真的只得 100 g（20% 水分），還能同時支持影片「&gt; 30 g 蛋白質／100 g」的說法嗎？</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>提示：在任一空白格自己打公式：固形物 = 500 × (1 − 0.73)；成品重 = 固形物 ÷ (1 − 0.20)；產率 = 成品重 ÷ 500 × 100。第 (3) 小題：先算 100 g 成品裡「該有」多少固形物，再和 500 g 鮮肉實際有多少固形物比較。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="B5" s="42" t="inlineStr"/>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="B7" s="41" t="inlineStr">
+        <is>
+          <t>問題 2：濕基／乾基練習：空盤 22.3300 g；盤+樣品 26.3300 g；乾燥後 25.5300 g。算出濕基 % 與乾基 %，並說明兩個數字為什麼不一樣。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>提示：把「2_濕基乾基」C9–C11 改成這三個數字，讀 C15、C16。做完記得改回 25.1234／28.1234／27.9734。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="B9" s="42" t="inlineStr"/>
+    </row>
+    <row r="11" ht="48" customHeight="1">
+      <c r="B11" s="41" t="inlineStr">
+        <is>
+          <t>問題 3：恆重判斷：連續三次乾燥後秤重 12.4050 g → 12.3890 g → 12.3860 g。(1) 第 3 次秤重後達到恆重了嗎？(2) 如果還沒，下一步該做什麼？(3) 再烘一次後第 4 次秤得 12.3851 g，現在恆重了嗎？該用哪一個重量算水分？</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>提示：把「2_濕基乾基」C23–C25 改成這三個數字，看 C28 的判定。第 (3) 小題：把 C23–C25 改成第 2、3、4 次的重量（12.3890、12.3860、12.3851）再看一次判定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1">
+      <c r="B13" s="42" t="inlineStr"/>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="B15" s="41" t="inlineStr">
+        <is>
+          <t>問題 4：比較「4_各組統計」各食品的 RSD%，哪一種食品精密度看起來最差？可能是操作的原因，還是樣品本身的原因？</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>提示：看 D11 的答案，再比較該食品的 SD（E 欄）是否真的比別的食品大。RSD = SD ÷ 平均，平均很小時 RSD 會被放大。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1">
+      <c r="B17" s="42" t="inlineStr"/>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="B19" s="41" t="inlineStr">
+        <is>
+          <t>問題 5：牛肉乾與龍眼乾水分都約 20%，但 aw 不同。哪一個比較容易發黴？請用「6_水活性」的微生物下限說明。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>提示：看 H、J 欄的平均 aw 與判定，並對照下面的散佈圖。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1">
+      <c r="B21" s="42" t="inlineStr"/>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="B23" s="41" t="inlineStr">
+        <is>
+          <t>問題 6：「5_烘箱vs紅外線」為什麼要用「成對」t 檢定，而不是把烘箱法 15 個值和紅外線 15 個值當成兩組獨立數據比較？試試看把 T.TEST 的最後一個參數從 1（成對）改成 2（兩組獨立、等變異），p 值怎麼變？為什麼？</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t>提示：在 J12 旁邊的空白格打 =T.TEST(E5:E19,D5:D19,2,2)。提示：15 份樣品的水分從 1% 到 35%，兩組各自的 SD 很大。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="60" customHeight="1">
+      <c r="B25" s="42" t="inlineStr"/>
+    </row>
+    <row r="27" ht="48" customHeight="1">
+      <c r="B27" s="41" t="inlineStr">
+        <is>
+          <t>問題 7：等溫吸濕曲線（「8_吸濕曲線」）：(1) ② 的 BET 為什麼不能用？請同時用「範圍內的點數」和「C 的正負號」說明。(2) 把 N30 的 σ 改成 0.003 和 0.008，Xm 可接受範圍各是多少？(3) 用 3–5 句話寫出這組數據的 MSI 結論：Xm 該怎麼報告、建議補做哪些飽和鹽、這組數據能可靠回答什麼問題。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>提示：飽和鹽 aw（25 °C）：LiCl 0.113、CH₃COOK 0.225、MgCl₂ 0.328、K₂CO₃ 0.432、Mg(NO₃)₂ 0.529。BET 至少要 3 點落在 aw 0.05–0.45。⑥ 的內插值就是「能可靠回答的問題」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1">
+      <c r="B29" s="72" t="n"/>
+    </row>
+    <row r="30"/>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -6823,7 +7682,7 @@
           <t>恆重判準（連續兩次秤重差 ≤）</t>
         </is>
       </c>
-      <c r="C5" s="22" t="n">
+      <c r="C5" s="47" t="n">
         <v>2</v>
       </c>
       <c r="D5" s="21" t="inlineStr">
@@ -6872,7 +7731,7 @@
           <t>空盤重</t>
         </is>
       </c>
-      <c r="C9" s="23" t="n">
+      <c r="C9" s="48" t="n">
         <v>25.1234</v>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -6892,7 +7751,7 @@
           <t>盤 + 樣品重</t>
         </is>
       </c>
-      <c r="C10" s="23" t="n">
+      <c r="C10" s="48" t="n">
         <v>28.1234</v>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -6912,7 +7771,7 @@
           <t>乾燥後（盤 + 乾樣品）重</t>
         </is>
       </c>
-      <c r="C11" s="23" t="n">
+      <c r="C11" s="48" t="n">
         <v>27.9734</v>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -6932,7 +7791,7 @@
           <t>樣品濕重 W濕</t>
         </is>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="43">
         <f>C10-C9</f>
         <v/>
       </c>
@@ -6953,7 +7812,7 @@
           <t>水分重</t>
         </is>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="43">
         <f>C10-C11</f>
         <v/>
       </c>
@@ -6974,7 +7833,7 @@
           <t>乾固形物重 W乾</t>
         </is>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="43">
         <f>C11-C9</f>
         <v/>
       </c>
@@ -7094,7 +7953,7 @@
           <t>第 1 次乾燥後重</t>
         </is>
       </c>
-      <c r="C23" s="23" t="n">
+      <c r="C23" s="48" t="n">
         <v>17.6698</v>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -7114,7 +7973,7 @@
           <t>第 2 次乾燥後重</t>
         </is>
       </c>
-      <c r="C24" s="23" t="n">
+      <c r="C24" s="48" t="n">
         <v>17.6634</v>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -7130,7 +7989,7 @@
           <t>第 3 次乾燥後重（沒有就留空）</t>
         </is>
       </c>
-      <c r="C25" s="23" t="n">
+      <c r="C25" s="48" t="n">
         <v>17.6623</v>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -7150,7 +8009,7 @@
           <t>第 1→2 次差</t>
         </is>
       </c>
-      <c r="C26" s="25">
+      <c r="C26" s="49">
         <f>ROUND(ABS(C24-C23)*1000,1)</f>
         <v/>
       </c>
@@ -7171,7 +8030,7 @@
           <t>第 2→3 次差</t>
         </is>
       </c>
-      <c r="C27" s="25">
+      <c r="C27" s="49">
         <f>IF(C25="","",ROUND(ABS(C25-C24)*1000,1))</f>
         <v/>
       </c>
@@ -7209,7 +8068,7 @@
           <t>計算水分要用的乾重</t>
         </is>
       </c>
-      <c r="C29" s="28">
+      <c r="C29" s="50">
         <f>IF(C26&lt;='2_濕基乾基'!$C$5,C24,IF(C25="",C24,C25))</f>
         <v/>
       </c>
@@ -7227,8 +8086,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B19:E19"/>
+    <mergeCell ref="C28:D28"/>
     <mergeCell ref="B2:E2"/>
-    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -7412,31 +8271,31 @@
           <t>beef_jerky</t>
         </is>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B5,'1_原始數據'!$I$2:$I$1000,$C5,'1_原始數據'!$C$2:$C$1000,D$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B5,'1_原始數據'!$I$2:$I$1000,$C5,'1_原始數據'!$C$2:$C$1000,D$3))</f>
         <v/>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B5,'1_原始數據'!$I$2:$I$1000,$C5,'1_原始數據'!$C$2:$C$1000,E$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B5,'1_原始數據'!$I$2:$I$1000,$C5,'1_原始數據'!$C$2:$C$1000,E$3))</f>
         <v/>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B5,'1_原始數據'!$I$2:$I$1000,$C5,'1_原始數據'!$C$2:$C$1000,F$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B5,'1_原始數據'!$I$2:$I$1000,$C5,'1_原始數據'!$C$2:$C$1000,F$3))</f>
         <v/>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B5,'1_原始數據'!$I$2:$I$1000,$C5,'1_原始數據'!$C$2:$C$1000,G$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B5,'1_原始數據'!$I$2:$I$1000,$C5,'1_原始數據'!$C$2:$C$1000,G$3))</f>
         <v/>
       </c>
-      <c r="H5" s="11">
+      <c r="H5" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B5,'1_原始數據'!$I$2:$I$1000,$C5,'1_原始數據'!$C$2:$C$1000,H$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B5,'1_原始數據'!$I$2:$I$1000,$C5,'1_原始數據'!$C$2:$C$1000,H$3))</f>
         <v/>
       </c>
-      <c r="I5" s="25">
+      <c r="I5" s="49">
         <f>ROUND(ABS(G5-F5)*1000,1)</f>
         <v/>
       </c>
-      <c r="J5" s="25">
+      <c r="J5" s="49">
         <f>IF(H5="","",ROUND(ABS(H5-G5)*1000,1))</f>
         <v/>
       </c>
@@ -7448,19 +8307,19 @@
         <f>IF(I5&lt;='2_濕基乾基'!$C$5,2,IF(H5="",2,3))</f>
         <v/>
       </c>
-      <c r="M5" s="11">
+      <c r="M5" s="43">
         <f>IF(L5=3,H5,G5)</f>
         <v/>
       </c>
-      <c r="N5" s="11">
+      <c r="N5" s="43">
         <f>E5-D5</f>
         <v/>
       </c>
-      <c r="O5" s="11">
+      <c r="O5" s="43">
         <f>E5-M5</f>
         <v/>
       </c>
-      <c r="P5" s="11">
+      <c r="P5" s="43">
         <f>M5-D5</f>
         <v/>
       </c>
@@ -7487,31 +8346,31 @@
           <t>beef_jerky</t>
         </is>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B6,'1_原始數據'!$I$2:$I$1000,$C6,'1_原始數據'!$C$2:$C$1000,D$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B6,'1_原始數據'!$I$2:$I$1000,$C6,'1_原始數據'!$C$2:$C$1000,D$3))</f>
         <v/>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B6,'1_原始數據'!$I$2:$I$1000,$C6,'1_原始數據'!$C$2:$C$1000,E$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B6,'1_原始數據'!$I$2:$I$1000,$C6,'1_原始數據'!$C$2:$C$1000,E$3))</f>
         <v/>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B6,'1_原始數據'!$I$2:$I$1000,$C6,'1_原始數據'!$C$2:$C$1000,F$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B6,'1_原始數據'!$I$2:$I$1000,$C6,'1_原始數據'!$C$2:$C$1000,F$3))</f>
         <v/>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B6,'1_原始數據'!$I$2:$I$1000,$C6,'1_原始數據'!$C$2:$C$1000,G$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B6,'1_原始數據'!$I$2:$I$1000,$C6,'1_原始數據'!$C$2:$C$1000,G$3))</f>
         <v/>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B6,'1_原始數據'!$I$2:$I$1000,$C6,'1_原始數據'!$C$2:$C$1000,H$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B6,'1_原始數據'!$I$2:$I$1000,$C6,'1_原始數據'!$C$2:$C$1000,H$3))</f>
         <v/>
       </c>
-      <c r="I6" s="25">
+      <c r="I6" s="49">
         <f>ROUND(ABS(G6-F6)*1000,1)</f>
         <v/>
       </c>
-      <c r="J6" s="25">
+      <c r="J6" s="49">
         <f>IF(H6="","",ROUND(ABS(H6-G6)*1000,1))</f>
         <v/>
       </c>
@@ -7523,19 +8382,19 @@
         <f>IF(I6&lt;='2_濕基乾基'!$C$5,2,IF(H6="",2,3))</f>
         <v/>
       </c>
-      <c r="M6" s="11">
+      <c r="M6" s="43">
         <f>IF(L6=3,H6,G6)</f>
         <v/>
       </c>
-      <c r="N6" s="11">
+      <c r="N6" s="43">
         <f>E6-D6</f>
         <v/>
       </c>
-      <c r="O6" s="11">
+      <c r="O6" s="43">
         <f>E6-M6</f>
         <v/>
       </c>
-      <c r="P6" s="11">
+      <c r="P6" s="43">
         <f>M6-D6</f>
         <v/>
       </c>
@@ -7562,31 +8421,31 @@
           <t>beef_jerky</t>
         </is>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B7,'1_原始數據'!$I$2:$I$1000,$C7,'1_原始數據'!$C$2:$C$1000,D$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B7,'1_原始數據'!$I$2:$I$1000,$C7,'1_原始數據'!$C$2:$C$1000,D$3))</f>
         <v/>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B7,'1_原始數據'!$I$2:$I$1000,$C7,'1_原始數據'!$C$2:$C$1000,E$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B7,'1_原始數據'!$I$2:$I$1000,$C7,'1_原始數據'!$C$2:$C$1000,E$3))</f>
         <v/>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B7,'1_原始數據'!$I$2:$I$1000,$C7,'1_原始數據'!$C$2:$C$1000,F$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B7,'1_原始數據'!$I$2:$I$1000,$C7,'1_原始數據'!$C$2:$C$1000,F$3))</f>
         <v/>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B7,'1_原始數據'!$I$2:$I$1000,$C7,'1_原始數據'!$C$2:$C$1000,G$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B7,'1_原始數據'!$I$2:$I$1000,$C7,'1_原始數據'!$C$2:$C$1000,G$3))</f>
         <v/>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B7,'1_原始數據'!$I$2:$I$1000,$C7,'1_原始數據'!$C$2:$C$1000,H$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B7,'1_原始數據'!$I$2:$I$1000,$C7,'1_原始數據'!$C$2:$C$1000,H$3))</f>
         <v/>
       </c>
-      <c r="I7" s="25">
+      <c r="I7" s="49">
         <f>ROUND(ABS(G7-F7)*1000,1)</f>
         <v/>
       </c>
-      <c r="J7" s="25">
+      <c r="J7" s="49">
         <f>IF(H7="","",ROUND(ABS(H7-G7)*1000,1))</f>
         <v/>
       </c>
@@ -7598,19 +8457,19 @@
         <f>IF(I7&lt;='2_濕基乾基'!$C$5,2,IF(H7="",2,3))</f>
         <v/>
       </c>
-      <c r="M7" s="11">
+      <c r="M7" s="43">
         <f>IF(L7=3,H7,G7)</f>
         <v/>
       </c>
-      <c r="N7" s="11">
+      <c r="N7" s="43">
         <f>E7-D7</f>
         <v/>
       </c>
-      <c r="O7" s="11">
+      <c r="O7" s="43">
         <f>E7-M7</f>
         <v/>
       </c>
-      <c r="P7" s="11">
+      <c r="P7" s="43">
         <f>M7-D7</f>
         <v/>
       </c>
@@ -7637,31 +8496,31 @@
           <t>dried_longan</t>
         </is>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B8,'1_原始數據'!$I$2:$I$1000,$C8,'1_原始數據'!$C$2:$C$1000,D$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B8,'1_原始數據'!$I$2:$I$1000,$C8,'1_原始數據'!$C$2:$C$1000,D$3))</f>
         <v/>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B8,'1_原始數據'!$I$2:$I$1000,$C8,'1_原始數據'!$C$2:$C$1000,E$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B8,'1_原始數據'!$I$2:$I$1000,$C8,'1_原始數據'!$C$2:$C$1000,E$3))</f>
         <v/>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B8,'1_原始數據'!$I$2:$I$1000,$C8,'1_原始數據'!$C$2:$C$1000,F$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B8,'1_原始數據'!$I$2:$I$1000,$C8,'1_原始數據'!$C$2:$C$1000,F$3))</f>
         <v/>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B8,'1_原始數據'!$I$2:$I$1000,$C8,'1_原始數據'!$C$2:$C$1000,G$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B8,'1_原始數據'!$I$2:$I$1000,$C8,'1_原始數據'!$C$2:$C$1000,G$3))</f>
         <v/>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B8,'1_原始數據'!$I$2:$I$1000,$C8,'1_原始數據'!$C$2:$C$1000,H$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B8,'1_原始數據'!$I$2:$I$1000,$C8,'1_原始數據'!$C$2:$C$1000,H$3))</f>
         <v/>
       </c>
-      <c r="I8" s="25">
+      <c r="I8" s="49">
         <f>ROUND(ABS(G8-F8)*1000,1)</f>
         <v/>
       </c>
-      <c r="J8" s="25">
+      <c r="J8" s="49">
         <f>IF(H8="","",ROUND(ABS(H8-G8)*1000,1))</f>
         <v/>
       </c>
@@ -7673,19 +8532,19 @@
         <f>IF(I8&lt;='2_濕基乾基'!$C$5,2,IF(H8="",2,3))</f>
         <v/>
       </c>
-      <c r="M8" s="11">
+      <c r="M8" s="43">
         <f>IF(L8=3,H8,G8)</f>
         <v/>
       </c>
-      <c r="N8" s="11">
+      <c r="N8" s="43">
         <f>E8-D8</f>
         <v/>
       </c>
-      <c r="O8" s="11">
+      <c r="O8" s="43">
         <f>E8-M8</f>
         <v/>
       </c>
-      <c r="P8" s="11">
+      <c r="P8" s="43">
         <f>M8-D8</f>
         <v/>
       </c>
@@ -7712,31 +8571,31 @@
           <t>dried_longan</t>
         </is>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B9,'1_原始數據'!$I$2:$I$1000,$C9,'1_原始數據'!$C$2:$C$1000,D$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B9,'1_原始數據'!$I$2:$I$1000,$C9,'1_原始數據'!$C$2:$C$1000,D$3))</f>
         <v/>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B9,'1_原始數據'!$I$2:$I$1000,$C9,'1_原始數據'!$C$2:$C$1000,E$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B9,'1_原始數據'!$I$2:$I$1000,$C9,'1_原始數據'!$C$2:$C$1000,E$3))</f>
         <v/>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B9,'1_原始數據'!$I$2:$I$1000,$C9,'1_原始數據'!$C$2:$C$1000,F$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B9,'1_原始數據'!$I$2:$I$1000,$C9,'1_原始數據'!$C$2:$C$1000,F$3))</f>
         <v/>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B9,'1_原始數據'!$I$2:$I$1000,$C9,'1_原始數據'!$C$2:$C$1000,G$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B9,'1_原始數據'!$I$2:$I$1000,$C9,'1_原始數據'!$C$2:$C$1000,G$3))</f>
         <v/>
       </c>
-      <c r="H9" s="11">
+      <c r="H9" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B9,'1_原始數據'!$I$2:$I$1000,$C9,'1_原始數據'!$C$2:$C$1000,H$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B9,'1_原始數據'!$I$2:$I$1000,$C9,'1_原始數據'!$C$2:$C$1000,H$3))</f>
         <v/>
       </c>
-      <c r="I9" s="25">
+      <c r="I9" s="49">
         <f>ROUND(ABS(G9-F9)*1000,1)</f>
         <v/>
       </c>
-      <c r="J9" s="25">
+      <c r="J9" s="49">
         <f>IF(H9="","",ROUND(ABS(H9-G9)*1000,1))</f>
         <v/>
       </c>
@@ -7748,19 +8607,19 @@
         <f>IF(I9&lt;='2_濕基乾基'!$C$5,2,IF(H9="",2,3))</f>
         <v/>
       </c>
-      <c r="M9" s="11">
+      <c r="M9" s="43">
         <f>IF(L9=3,H9,G9)</f>
         <v/>
       </c>
-      <c r="N9" s="11">
+      <c r="N9" s="43">
         <f>E9-D9</f>
         <v/>
       </c>
-      <c r="O9" s="11">
+      <c r="O9" s="43">
         <f>E9-M9</f>
         <v/>
       </c>
-      <c r="P9" s="11">
+      <c r="P9" s="43">
         <f>M9-D9</f>
         <v/>
       </c>
@@ -7787,31 +8646,31 @@
           <t>dried_longan</t>
         </is>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B10,'1_原始數據'!$I$2:$I$1000,$C10,'1_原始數據'!$C$2:$C$1000,D$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B10,'1_原始數據'!$I$2:$I$1000,$C10,'1_原始數據'!$C$2:$C$1000,D$3))</f>
         <v/>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B10,'1_原始數據'!$I$2:$I$1000,$C10,'1_原始數據'!$C$2:$C$1000,E$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B10,'1_原始數據'!$I$2:$I$1000,$C10,'1_原始數據'!$C$2:$C$1000,E$3))</f>
         <v/>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B10,'1_原始數據'!$I$2:$I$1000,$C10,'1_原始數據'!$C$2:$C$1000,F$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B10,'1_原始數據'!$I$2:$I$1000,$C10,'1_原始數據'!$C$2:$C$1000,F$3))</f>
         <v/>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B10,'1_原始數據'!$I$2:$I$1000,$C10,'1_原始數據'!$C$2:$C$1000,G$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B10,'1_原始數據'!$I$2:$I$1000,$C10,'1_原始數據'!$C$2:$C$1000,G$3))</f>
         <v/>
       </c>
-      <c r="H10" s="11">
+      <c r="H10" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B10,'1_原始數據'!$I$2:$I$1000,$C10,'1_原始數據'!$C$2:$C$1000,H$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B10,'1_原始數據'!$I$2:$I$1000,$C10,'1_原始數據'!$C$2:$C$1000,H$3))</f>
         <v/>
       </c>
-      <c r="I10" s="25">
+      <c r="I10" s="49">
         <f>ROUND(ABS(G10-F10)*1000,1)</f>
         <v/>
       </c>
-      <c r="J10" s="25">
+      <c r="J10" s="49">
         <f>IF(H10="","",ROUND(ABS(H10-G10)*1000,1))</f>
         <v/>
       </c>
@@ -7823,19 +8682,19 @@
         <f>IF(I10&lt;='2_濕基乾基'!$C$5,2,IF(H10="",2,3))</f>
         <v/>
       </c>
-      <c r="M10" s="11">
+      <c r="M10" s="43">
         <f>IF(L10=3,H10,G10)</f>
         <v/>
       </c>
-      <c r="N10" s="11">
+      <c r="N10" s="43">
         <f>E10-D10</f>
         <v/>
       </c>
-      <c r="O10" s="11">
+      <c r="O10" s="43">
         <f>E10-M10</f>
         <v/>
       </c>
-      <c r="P10" s="11">
+      <c r="P10" s="43">
         <f>M10-D10</f>
         <v/>
       </c>
@@ -7862,31 +8721,31 @@
           <t>white_bread</t>
         </is>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B11,'1_原始數據'!$I$2:$I$1000,$C11,'1_原始數據'!$C$2:$C$1000,D$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B11,'1_原始數據'!$I$2:$I$1000,$C11,'1_原始數據'!$C$2:$C$1000,D$3))</f>
         <v/>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B11,'1_原始數據'!$I$2:$I$1000,$C11,'1_原始數據'!$C$2:$C$1000,E$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B11,'1_原始數據'!$I$2:$I$1000,$C11,'1_原始數據'!$C$2:$C$1000,E$3))</f>
         <v/>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B11,'1_原始數據'!$I$2:$I$1000,$C11,'1_原始數據'!$C$2:$C$1000,F$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B11,'1_原始數據'!$I$2:$I$1000,$C11,'1_原始數據'!$C$2:$C$1000,F$3))</f>
         <v/>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B11,'1_原始數據'!$I$2:$I$1000,$C11,'1_原始數據'!$C$2:$C$1000,G$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B11,'1_原始數據'!$I$2:$I$1000,$C11,'1_原始數據'!$C$2:$C$1000,G$3))</f>
         <v/>
       </c>
-      <c r="H11" s="11">
+      <c r="H11" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B11,'1_原始數據'!$I$2:$I$1000,$C11,'1_原始數據'!$C$2:$C$1000,H$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B11,'1_原始數據'!$I$2:$I$1000,$C11,'1_原始數據'!$C$2:$C$1000,H$3))</f>
         <v/>
       </c>
-      <c r="I11" s="25">
+      <c r="I11" s="49">
         <f>ROUND(ABS(G11-F11)*1000,1)</f>
         <v/>
       </c>
-      <c r="J11" s="25">
+      <c r="J11" s="49">
         <f>IF(H11="","",ROUND(ABS(H11-G11)*1000,1))</f>
         <v/>
       </c>
@@ -7898,19 +8757,19 @@
         <f>IF(I11&lt;='2_濕基乾基'!$C$5,2,IF(H11="",2,3))</f>
         <v/>
       </c>
-      <c r="M11" s="11">
+      <c r="M11" s="43">
         <f>IF(L11=3,H11,G11)</f>
         <v/>
       </c>
-      <c r="N11" s="11">
+      <c r="N11" s="43">
         <f>E11-D11</f>
         <v/>
       </c>
-      <c r="O11" s="11">
+      <c r="O11" s="43">
         <f>E11-M11</f>
         <v/>
       </c>
-      <c r="P11" s="11">
+      <c r="P11" s="43">
         <f>M11-D11</f>
         <v/>
       </c>
@@ -7937,31 +8796,31 @@
           <t>white_bread</t>
         </is>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B12,'1_原始數據'!$I$2:$I$1000,$C12,'1_原始數據'!$C$2:$C$1000,D$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B12,'1_原始數據'!$I$2:$I$1000,$C12,'1_原始數據'!$C$2:$C$1000,D$3))</f>
         <v/>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B12,'1_原始數據'!$I$2:$I$1000,$C12,'1_原始數據'!$C$2:$C$1000,E$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B12,'1_原始數據'!$I$2:$I$1000,$C12,'1_原始數據'!$C$2:$C$1000,E$3))</f>
         <v/>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B12,'1_原始數據'!$I$2:$I$1000,$C12,'1_原始數據'!$C$2:$C$1000,F$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B12,'1_原始數據'!$I$2:$I$1000,$C12,'1_原始數據'!$C$2:$C$1000,F$3))</f>
         <v/>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B12,'1_原始數據'!$I$2:$I$1000,$C12,'1_原始數據'!$C$2:$C$1000,G$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B12,'1_原始數據'!$I$2:$I$1000,$C12,'1_原始數據'!$C$2:$C$1000,G$3))</f>
         <v/>
       </c>
-      <c r="H12" s="11">
+      <c r="H12" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B12,'1_原始數據'!$I$2:$I$1000,$C12,'1_原始數據'!$C$2:$C$1000,H$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B12,'1_原始數據'!$I$2:$I$1000,$C12,'1_原始數據'!$C$2:$C$1000,H$3))</f>
         <v/>
       </c>
-      <c r="I12" s="25">
+      <c r="I12" s="49">
         <f>ROUND(ABS(G12-F12)*1000,1)</f>
         <v/>
       </c>
-      <c r="J12" s="25">
+      <c r="J12" s="49">
         <f>IF(H12="","",ROUND(ABS(H12-G12)*1000,1))</f>
         <v/>
       </c>
@@ -7973,19 +8832,19 @@
         <f>IF(I12&lt;='2_濕基乾基'!$C$5,2,IF(H12="",2,3))</f>
         <v/>
       </c>
-      <c r="M12" s="11">
+      <c r="M12" s="43">
         <f>IF(L12=3,H12,G12)</f>
         <v/>
       </c>
-      <c r="N12" s="11">
+      <c r="N12" s="43">
         <f>E12-D12</f>
         <v/>
       </c>
-      <c r="O12" s="11">
+      <c r="O12" s="43">
         <f>E12-M12</f>
         <v/>
       </c>
-      <c r="P12" s="11">
+      <c r="P12" s="43">
         <f>M12-D12</f>
         <v/>
       </c>
@@ -8012,31 +8871,31 @@
           <t>white_bread</t>
         </is>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B13,'1_原始數據'!$I$2:$I$1000,$C13,'1_原始數據'!$C$2:$C$1000,D$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B13,'1_原始數據'!$I$2:$I$1000,$C13,'1_原始數據'!$C$2:$C$1000,D$3))</f>
         <v/>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B13,'1_原始數據'!$I$2:$I$1000,$C13,'1_原始數據'!$C$2:$C$1000,E$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B13,'1_原始數據'!$I$2:$I$1000,$C13,'1_原始數據'!$C$2:$C$1000,E$3))</f>
         <v/>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B13,'1_原始數據'!$I$2:$I$1000,$C13,'1_原始數據'!$C$2:$C$1000,F$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B13,'1_原始數據'!$I$2:$I$1000,$C13,'1_原始數據'!$C$2:$C$1000,F$3))</f>
         <v/>
       </c>
-      <c r="G13" s="11">
+      <c r="G13" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B13,'1_原始數據'!$I$2:$I$1000,$C13,'1_原始數據'!$C$2:$C$1000,G$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B13,'1_原始數據'!$I$2:$I$1000,$C13,'1_原始數據'!$C$2:$C$1000,G$3))</f>
         <v/>
       </c>
-      <c r="H13" s="11">
+      <c r="H13" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B13,'1_原始數據'!$I$2:$I$1000,$C13,'1_原始數據'!$C$2:$C$1000,H$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B13,'1_原始數據'!$I$2:$I$1000,$C13,'1_原始數據'!$C$2:$C$1000,H$3))</f>
         <v/>
       </c>
-      <c r="I13" s="25">
+      <c r="I13" s="49">
         <f>ROUND(ABS(G13-F13)*1000,1)</f>
         <v/>
       </c>
-      <c r="J13" s="25">
+      <c r="J13" s="49">
         <f>IF(H13="","",ROUND(ABS(H13-G13)*1000,1))</f>
         <v/>
       </c>
@@ -8048,19 +8907,19 @@
         <f>IF(I13&lt;='2_濕基乾基'!$C$5,2,IF(H13="",2,3))</f>
         <v/>
       </c>
-      <c r="M13" s="11">
+      <c r="M13" s="43">
         <f>IF(L13=3,H13,G13)</f>
         <v/>
       </c>
-      <c r="N13" s="11">
+      <c r="N13" s="43">
         <f>E13-D13</f>
         <v/>
       </c>
-      <c r="O13" s="11">
+      <c r="O13" s="43">
         <f>E13-M13</f>
         <v/>
       </c>
-      <c r="P13" s="11">
+      <c r="P13" s="43">
         <f>M13-D13</f>
         <v/>
       </c>
@@ -8087,31 +8946,31 @@
           <t>potato_chips</t>
         </is>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B14,'1_原始數據'!$I$2:$I$1000,$C14,'1_原始數據'!$C$2:$C$1000,D$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B14,'1_原始數據'!$I$2:$I$1000,$C14,'1_原始數據'!$C$2:$C$1000,D$3))</f>
         <v/>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B14,'1_原始數據'!$I$2:$I$1000,$C14,'1_原始數據'!$C$2:$C$1000,E$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B14,'1_原始數據'!$I$2:$I$1000,$C14,'1_原始數據'!$C$2:$C$1000,E$3))</f>
         <v/>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B14,'1_原始數據'!$I$2:$I$1000,$C14,'1_原始數據'!$C$2:$C$1000,F$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B14,'1_原始數據'!$I$2:$I$1000,$C14,'1_原始數據'!$C$2:$C$1000,F$3))</f>
         <v/>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B14,'1_原始數據'!$I$2:$I$1000,$C14,'1_原始數據'!$C$2:$C$1000,G$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B14,'1_原始數據'!$I$2:$I$1000,$C14,'1_原始數據'!$C$2:$C$1000,G$3))</f>
         <v/>
       </c>
-      <c r="H14" s="11">
+      <c r="H14" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B14,'1_原始數據'!$I$2:$I$1000,$C14,'1_原始數據'!$C$2:$C$1000,H$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B14,'1_原始數據'!$I$2:$I$1000,$C14,'1_原始數據'!$C$2:$C$1000,H$3))</f>
         <v/>
       </c>
-      <c r="I14" s="25">
+      <c r="I14" s="49">
         <f>ROUND(ABS(G14-F14)*1000,1)</f>
         <v/>
       </c>
-      <c r="J14" s="25">
+      <c r="J14" s="49">
         <f>IF(H14="","",ROUND(ABS(H14-G14)*1000,1))</f>
         <v/>
       </c>
@@ -8123,19 +8982,19 @@
         <f>IF(I14&lt;='2_濕基乾基'!$C$5,2,IF(H14="",2,3))</f>
         <v/>
       </c>
-      <c r="M14" s="11">
+      <c r="M14" s="43">
         <f>IF(L14=3,H14,G14)</f>
         <v/>
       </c>
-      <c r="N14" s="11">
+      <c r="N14" s="43">
         <f>E14-D14</f>
         <v/>
       </c>
-      <c r="O14" s="11">
+      <c r="O14" s="43">
         <f>E14-M14</f>
         <v/>
       </c>
-      <c r="P14" s="11">
+      <c r="P14" s="43">
         <f>M14-D14</f>
         <v/>
       </c>
@@ -8162,31 +9021,31 @@
           <t>potato_chips</t>
         </is>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B15,'1_原始數據'!$I$2:$I$1000,$C15,'1_原始數據'!$C$2:$C$1000,D$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B15,'1_原始數據'!$I$2:$I$1000,$C15,'1_原始數據'!$C$2:$C$1000,D$3))</f>
         <v/>
       </c>
-      <c r="E15" s="11">
+      <c r="E15" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B15,'1_原始數據'!$I$2:$I$1000,$C15,'1_原始數據'!$C$2:$C$1000,E$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B15,'1_原始數據'!$I$2:$I$1000,$C15,'1_原始數據'!$C$2:$C$1000,E$3))</f>
         <v/>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B15,'1_原始數據'!$I$2:$I$1000,$C15,'1_原始數據'!$C$2:$C$1000,F$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B15,'1_原始數據'!$I$2:$I$1000,$C15,'1_原始數據'!$C$2:$C$1000,F$3))</f>
         <v/>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B15,'1_原始數據'!$I$2:$I$1000,$C15,'1_原始數據'!$C$2:$C$1000,G$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B15,'1_原始數據'!$I$2:$I$1000,$C15,'1_原始數據'!$C$2:$C$1000,G$3))</f>
         <v/>
       </c>
-      <c r="H15" s="11">
+      <c r="H15" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B15,'1_原始數據'!$I$2:$I$1000,$C15,'1_原始數據'!$C$2:$C$1000,H$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B15,'1_原始數據'!$I$2:$I$1000,$C15,'1_原始數據'!$C$2:$C$1000,H$3))</f>
         <v/>
       </c>
-      <c r="I15" s="25">
+      <c r="I15" s="49">
         <f>ROUND(ABS(G15-F15)*1000,1)</f>
         <v/>
       </c>
-      <c r="J15" s="25">
+      <c r="J15" s="49">
         <f>IF(H15="","",ROUND(ABS(H15-G15)*1000,1))</f>
         <v/>
       </c>
@@ -8198,19 +9057,19 @@
         <f>IF(I15&lt;='2_濕基乾基'!$C$5,2,IF(H15="",2,3))</f>
         <v/>
       </c>
-      <c r="M15" s="11">
+      <c r="M15" s="43">
         <f>IF(L15=3,H15,G15)</f>
         <v/>
       </c>
-      <c r="N15" s="11">
+      <c r="N15" s="43">
         <f>E15-D15</f>
         <v/>
       </c>
-      <c r="O15" s="11">
+      <c r="O15" s="43">
         <f>E15-M15</f>
         <v/>
       </c>
-      <c r="P15" s="11">
+      <c r="P15" s="43">
         <f>M15-D15</f>
         <v/>
       </c>
@@ -8237,31 +9096,31 @@
           <t>potato_chips</t>
         </is>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B16,'1_原始數據'!$I$2:$I$1000,$C16,'1_原始數據'!$C$2:$C$1000,D$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B16,'1_原始數據'!$I$2:$I$1000,$C16,'1_原始數據'!$C$2:$C$1000,D$3))</f>
         <v/>
       </c>
-      <c r="E16" s="11">
+      <c r="E16" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B16,'1_原始數據'!$I$2:$I$1000,$C16,'1_原始數據'!$C$2:$C$1000,E$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B16,'1_原始數據'!$I$2:$I$1000,$C16,'1_原始數據'!$C$2:$C$1000,E$3))</f>
         <v/>
       </c>
-      <c r="F16" s="11">
+      <c r="F16" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B16,'1_原始數據'!$I$2:$I$1000,$C16,'1_原始數據'!$C$2:$C$1000,F$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B16,'1_原始數據'!$I$2:$I$1000,$C16,'1_原始數據'!$C$2:$C$1000,F$3))</f>
         <v/>
       </c>
-      <c r="G16" s="11">
+      <c r="G16" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B16,'1_原始數據'!$I$2:$I$1000,$C16,'1_原始數據'!$C$2:$C$1000,G$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B16,'1_原始數據'!$I$2:$I$1000,$C16,'1_原始數據'!$C$2:$C$1000,G$3))</f>
         <v/>
       </c>
-      <c r="H16" s="11">
+      <c r="H16" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B16,'1_原始數據'!$I$2:$I$1000,$C16,'1_原始數據'!$C$2:$C$1000,H$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B16,'1_原始數據'!$I$2:$I$1000,$C16,'1_原始數據'!$C$2:$C$1000,H$3))</f>
         <v/>
       </c>
-      <c r="I16" s="25">
+      <c r="I16" s="49">
         <f>ROUND(ABS(G16-F16)*1000,1)</f>
         <v/>
       </c>
-      <c r="J16" s="25">
+      <c r="J16" s="49">
         <f>IF(H16="","",ROUND(ABS(H16-G16)*1000,1))</f>
         <v/>
       </c>
@@ -8273,19 +9132,19 @@
         <f>IF(I16&lt;='2_濕基乾基'!$C$5,2,IF(H16="",2,3))</f>
         <v/>
       </c>
-      <c r="M16" s="11">
+      <c r="M16" s="43">
         <f>IF(L16=3,H16,G16)</f>
         <v/>
       </c>
-      <c r="N16" s="11">
+      <c r="N16" s="43">
         <f>E16-D16</f>
         <v/>
       </c>
-      <c r="O16" s="11">
+      <c r="O16" s="43">
         <f>E16-M16</f>
         <v/>
       </c>
-      <c r="P16" s="11">
+      <c r="P16" s="43">
         <f>M16-D16</f>
         <v/>
       </c>
@@ -8312,31 +9171,31 @@
           <t>milk_powder</t>
         </is>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B17,'1_原始數據'!$I$2:$I$1000,$C17,'1_原始數據'!$C$2:$C$1000,D$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B17,'1_原始數據'!$I$2:$I$1000,$C17,'1_原始數據'!$C$2:$C$1000,D$3))</f>
         <v/>
       </c>
-      <c r="E17" s="11">
+      <c r="E17" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B17,'1_原始數據'!$I$2:$I$1000,$C17,'1_原始數據'!$C$2:$C$1000,E$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B17,'1_原始數據'!$I$2:$I$1000,$C17,'1_原始數據'!$C$2:$C$1000,E$3))</f>
         <v/>
       </c>
-      <c r="F17" s="11">
+      <c r="F17" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B17,'1_原始數據'!$I$2:$I$1000,$C17,'1_原始數據'!$C$2:$C$1000,F$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B17,'1_原始數據'!$I$2:$I$1000,$C17,'1_原始數據'!$C$2:$C$1000,F$3))</f>
         <v/>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B17,'1_原始數據'!$I$2:$I$1000,$C17,'1_原始數據'!$C$2:$C$1000,G$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B17,'1_原始數據'!$I$2:$I$1000,$C17,'1_原始數據'!$C$2:$C$1000,G$3))</f>
         <v/>
       </c>
-      <c r="H17" s="11">
+      <c r="H17" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B17,'1_原始數據'!$I$2:$I$1000,$C17,'1_原始數據'!$C$2:$C$1000,H$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B17,'1_原始數據'!$I$2:$I$1000,$C17,'1_原始數據'!$C$2:$C$1000,H$3))</f>
         <v/>
       </c>
-      <c r="I17" s="25">
+      <c r="I17" s="49">
         <f>ROUND(ABS(G17-F17)*1000,1)</f>
         <v/>
       </c>
-      <c r="J17" s="25">
+      <c r="J17" s="49">
         <f>IF(H17="","",ROUND(ABS(H17-G17)*1000,1))</f>
         <v/>
       </c>
@@ -8348,19 +9207,19 @@
         <f>IF(I17&lt;='2_濕基乾基'!$C$5,2,IF(H17="",2,3))</f>
         <v/>
       </c>
-      <c r="M17" s="11">
+      <c r="M17" s="43">
         <f>IF(L17=3,H17,G17)</f>
         <v/>
       </c>
-      <c r="N17" s="11">
+      <c r="N17" s="43">
         <f>E17-D17</f>
         <v/>
       </c>
-      <c r="O17" s="11">
+      <c r="O17" s="43">
         <f>E17-M17</f>
         <v/>
       </c>
-      <c r="P17" s="11">
+      <c r="P17" s="43">
         <f>M17-D17</f>
         <v/>
       </c>
@@ -8387,31 +9246,31 @@
           <t>milk_powder</t>
         </is>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B18,'1_原始數據'!$I$2:$I$1000,$C18,'1_原始數據'!$C$2:$C$1000,D$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B18,'1_原始數據'!$I$2:$I$1000,$C18,'1_原始數據'!$C$2:$C$1000,D$3))</f>
         <v/>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B18,'1_原始數據'!$I$2:$I$1000,$C18,'1_原始數據'!$C$2:$C$1000,E$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B18,'1_原始數據'!$I$2:$I$1000,$C18,'1_原始數據'!$C$2:$C$1000,E$3))</f>
         <v/>
       </c>
-      <c r="F18" s="11">
+      <c r="F18" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B18,'1_原始數據'!$I$2:$I$1000,$C18,'1_原始數據'!$C$2:$C$1000,F$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B18,'1_原始數據'!$I$2:$I$1000,$C18,'1_原始數據'!$C$2:$C$1000,F$3))</f>
         <v/>
       </c>
-      <c r="G18" s="11">
+      <c r="G18" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B18,'1_原始數據'!$I$2:$I$1000,$C18,'1_原始數據'!$C$2:$C$1000,G$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B18,'1_原始數據'!$I$2:$I$1000,$C18,'1_原始數據'!$C$2:$C$1000,G$3))</f>
         <v/>
       </c>
-      <c r="H18" s="11">
+      <c r="H18" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B18,'1_原始數據'!$I$2:$I$1000,$C18,'1_原始數據'!$C$2:$C$1000,H$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B18,'1_原始數據'!$I$2:$I$1000,$C18,'1_原始數據'!$C$2:$C$1000,H$3))</f>
         <v/>
       </c>
-      <c r="I18" s="25">
+      <c r="I18" s="49">
         <f>ROUND(ABS(G18-F18)*1000,1)</f>
         <v/>
       </c>
-      <c r="J18" s="25">
+      <c r="J18" s="49">
         <f>IF(H18="","",ROUND(ABS(H18-G18)*1000,1))</f>
         <v/>
       </c>
@@ -8423,19 +9282,19 @@
         <f>IF(I18&lt;='2_濕基乾基'!$C$5,2,IF(H18="",2,3))</f>
         <v/>
       </c>
-      <c r="M18" s="11">
+      <c r="M18" s="43">
         <f>IF(L18=3,H18,G18)</f>
         <v/>
       </c>
-      <c r="N18" s="11">
+      <c r="N18" s="43">
         <f>E18-D18</f>
         <v/>
       </c>
-      <c r="O18" s="11">
+      <c r="O18" s="43">
         <f>E18-M18</f>
         <v/>
       </c>
-      <c r="P18" s="11">
+      <c r="P18" s="43">
         <f>M18-D18</f>
         <v/>
       </c>
@@ -8462,31 +9321,31 @@
           <t>milk_powder</t>
         </is>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B19,'1_原始數據'!$I$2:$I$1000,$C19,'1_原始數據'!$C$2:$C$1000,D$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B19,'1_原始數據'!$I$2:$I$1000,$C19,'1_原始數據'!$C$2:$C$1000,D$3))</f>
         <v/>
       </c>
-      <c r="E19" s="11">
+      <c r="E19" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B19,'1_原始數據'!$I$2:$I$1000,$C19,'1_原始數據'!$C$2:$C$1000,E$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B19,'1_原始數據'!$I$2:$I$1000,$C19,'1_原始數據'!$C$2:$C$1000,E$3))</f>
         <v/>
       </c>
-      <c r="F19" s="11">
+      <c r="F19" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B19,'1_原始數據'!$I$2:$I$1000,$C19,'1_原始數據'!$C$2:$C$1000,F$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B19,'1_原始數據'!$I$2:$I$1000,$C19,'1_原始數據'!$C$2:$C$1000,F$3))</f>
         <v/>
       </c>
-      <c r="G19" s="11">
+      <c r="G19" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B19,'1_原始數據'!$I$2:$I$1000,$C19,'1_原始數據'!$C$2:$C$1000,G$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B19,'1_原始數據'!$I$2:$I$1000,$C19,'1_原始數據'!$C$2:$C$1000,G$3))</f>
         <v/>
       </c>
-      <c r="H19" s="11">
+      <c r="H19" s="43">
         <f>IF(COUNTIFS('1_原始數據'!$B$2:$B$1000,$B19,'1_原始數據'!$I$2:$I$1000,$C19,'1_原始數據'!$C$2:$C$1000,H$3)=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$B$2:$B$1000,$B19,'1_原始數據'!$I$2:$I$1000,$C19,'1_原始數據'!$C$2:$C$1000,H$3))</f>
         <v/>
       </c>
-      <c r="I19" s="25">
+      <c r="I19" s="49">
         <f>ROUND(ABS(G19-F19)*1000,1)</f>
         <v/>
       </c>
-      <c r="J19" s="25">
+      <c r="J19" s="49">
         <f>IF(H19="","",ROUND(ABS(H19-G19)*1000,1))</f>
         <v/>
       </c>
@@ -8498,19 +9357,19 @@
         <f>IF(I19&lt;='2_濕基乾基'!$C$5,2,IF(H19="",2,3))</f>
         <v/>
       </c>
-      <c r="M19" s="11">
+      <c r="M19" s="43">
         <f>IF(L19=3,H19,G19)</f>
         <v/>
       </c>
-      <c r="N19" s="11">
+      <c r="N19" s="43">
         <f>E19-D19</f>
         <v/>
       </c>
-      <c r="O19" s="11">
+      <c r="O19" s="43">
         <f>E19-M19</f>
         <v/>
       </c>
-      <c r="P19" s="11">
+      <c r="P19" s="43">
         <f>M19-D19</f>
         <v/>
       </c>
@@ -8714,7 +9573,7 @@
         <f>AVERAGEIFS('3_烘箱法恆重'!$Q$5:$Q$19,'3_烘箱法恆重'!$A$5:$A$19,A5,'3_烘箱法恆重'!$C$5:$C$19,B5)</f>
         <v/>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="45">
         <f t="array" ref="E5">_xlfn.STDEV.S(IF(('3_烘箱法恆重'!$A$5:$A$19=A5)*('3_烘箱法恆重'!$C$5:$C$19=B5),'3_烘箱法恆重'!$Q$5:$Q$19))</f>
         <v/>
       </c>
@@ -8745,7 +9604,7 @@
         <f>AVERAGEIFS('3_烘箱法恆重'!$Q$5:$Q$19,'3_烘箱法恆重'!$A$5:$A$19,A6,'3_烘箱法恆重'!$C$5:$C$19,B6)</f>
         <v/>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="45">
         <f t="array" ref="E6">_xlfn.STDEV.S(IF(('3_烘箱法恆重'!$A$5:$A$19=A6)*('3_烘箱法恆重'!$C$5:$C$19=B6),'3_烘箱法恆重'!$Q$5:$Q$19))</f>
         <v/>
       </c>
@@ -8776,7 +9635,7 @@
         <f>AVERAGEIFS('3_烘箱法恆重'!$Q$5:$Q$19,'3_烘箱法恆重'!$A$5:$A$19,A7,'3_烘箱法恆重'!$C$5:$C$19,B7)</f>
         <v/>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="45">
         <f t="array" ref="E7">_xlfn.STDEV.S(IF(('3_烘箱法恆重'!$A$5:$A$19=A7)*('3_烘箱法恆重'!$C$5:$C$19=B7),'3_烘箱法恆重'!$Q$5:$Q$19))</f>
         <v/>
       </c>
@@ -8807,7 +9666,7 @@
         <f>AVERAGEIFS('3_烘箱法恆重'!$Q$5:$Q$19,'3_烘箱法恆重'!$A$5:$A$19,A8,'3_烘箱法恆重'!$C$5:$C$19,B8)</f>
         <v/>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="45">
         <f t="array" ref="E8">_xlfn.STDEV.S(IF(('3_烘箱法恆重'!$A$5:$A$19=A8)*('3_烘箱法恆重'!$C$5:$C$19=B8),'3_烘箱法恆重'!$Q$5:$Q$19))</f>
         <v/>
       </c>
@@ -8833,7 +9692,7 @@
         <f>AVERAGEIFS('3_烘箱法恆重'!$Q$5:$Q$19,'3_烘箱法恆重'!$A$5:$A$19,A9,'3_烘箱法恆重'!$C$5:$C$19,B9)</f>
         <v/>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="45">
         <f t="array" ref="E9">_xlfn.STDEV.S(IF(('3_烘箱法恆重'!$A$5:$A$19=A9)*('3_烘箱法恆重'!$C$5:$C$19=B9),'3_烘箱法恆重'!$Q$5:$Q$19))</f>
         <v/>
       </c>
@@ -9046,11 +9905,11 @@
           <t>COUNT 數有幾個數字（幾對）</t>
         </is>
       </c>
-      <c r="M5" s="25">
+      <c r="M5" s="49">
         <f>0</f>
         <v/>
       </c>
-      <c r="N5" s="14">
+      <c r="N5" s="45">
         <f>$J$6</f>
         <v/>
       </c>
@@ -9102,11 +9961,11 @@
           <t>負值＝紅外線比烘箱法低。這就是紅外線水分計的偏差</t>
         </is>
       </c>
-      <c r="M6" s="25">
+      <c r="M6" s="49">
         <f>MAX(G5:G19)*1.05</f>
         <v/>
       </c>
-      <c r="N6" s="14">
+      <c r="N6" s="45">
         <f>$J$6</f>
         <v/>
       </c>
@@ -9149,7 +10008,7 @@
           <t>差的 SD s_d (%)</t>
         </is>
       </c>
-      <c r="J7" s="14">
+      <c r="J7" s="45">
         <f>_xlfn.STDEV.S(F5:F19)</f>
         <v/>
       </c>
@@ -9193,7 +10052,7 @@
           <t>平均差的標準誤 SE (%)</t>
         </is>
       </c>
-      <c r="J8" s="11">
+      <c r="J8" s="43">
         <f>J7/SQRT(J5)</f>
         <v/>
       </c>
@@ -9237,7 +10096,7 @@
           <t>t 值</t>
         </is>
       </c>
-      <c r="J9" s="35">
+      <c r="J9" s="51">
         <f>J6/J8</f>
         <v/>
       </c>
@@ -9413,7 +10272,7 @@
           <t>t 臨界值（95%）</t>
         </is>
       </c>
-      <c r="J13" s="14">
+      <c r="J13" s="45">
         <f>_xlfn.T.INV.2T(0.05,J10)</f>
         <v/>
       </c>
@@ -9790,7 +10649,7 @@
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A5,'1_原始數據'!$I$2:$I$1000,$B5,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A5,'1_原始數據'!$I$2:$I$1000,$B5,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey"))</f>
         <v/>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="45">
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A5,'1_原始數據'!$I$2:$I$1000,$B5,'1_原始數據'!$C$2:$C$1000,"aw_reading")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A5,'1_原始數據'!$I$2:$I$1000,$B5,'1_原始數據'!$C$2:$C$1000,"aw_reading"))</f>
         <v/>
       </c>
@@ -9824,7 +10683,7 @@
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A6,'1_原始數據'!$I$2:$I$1000,$B6,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A6,'1_原始數據'!$I$2:$I$1000,$B6,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey"))</f>
         <v/>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="45">
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A6,'1_原始數據'!$I$2:$I$1000,$B6,'1_原始數據'!$C$2:$C$1000,"aw_reading")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A6,'1_原始數據'!$I$2:$I$1000,$B6,'1_原始數據'!$C$2:$C$1000,"aw_reading"))</f>
         <v/>
       </c>
@@ -9836,7 +10695,7 @@
       <c r="G6" s="39" t="n">
         <v>0.88</v>
       </c>
-      <c r="L6" s="25">
+      <c r="L6" s="49">
         <f>MAX($C$5:$C$34)*1.1</f>
         <v/>
       </c>
@@ -9858,7 +10717,7 @@
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A7,'1_原始數據'!$I$2:$I$1000,$B7,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A7,'1_原始數據'!$I$2:$I$1000,$B7,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey"))</f>
         <v/>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="45">
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A7,'1_原始數據'!$I$2:$I$1000,$B7,'1_原始數據'!$C$2:$C$1000,"aw_reading")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A7,'1_原始數據'!$I$2:$I$1000,$B7,'1_原始數據'!$C$2:$C$1000,"aw_reading"))</f>
         <v/>
       </c>
@@ -9892,7 +10751,7 @@
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A8,'1_原始數據'!$I$2:$I$1000,$B8,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A8,'1_原始數據'!$I$2:$I$1000,$B8,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey"))</f>
         <v/>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="45">
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A8,'1_原始數據'!$I$2:$I$1000,$B8,'1_原始數據'!$C$2:$C$1000,"aw_reading")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A8,'1_原始數據'!$I$2:$I$1000,$B8,'1_原始數據'!$C$2:$C$1000,"aw_reading"))</f>
         <v/>
       </c>
@@ -9904,7 +10763,7 @@
       <c r="G8" s="39" t="n">
         <v>0.61</v>
       </c>
-      <c r="L8" s="25">
+      <c r="L8" s="49">
         <f>MAX($C$5:$C$34)*1.1</f>
         <v/>
       </c>
@@ -9926,7 +10785,7 @@
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A9,'1_原始數據'!$I$2:$I$1000,$B9,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A9,'1_原始數據'!$I$2:$I$1000,$B9,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey"))</f>
         <v/>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="45">
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A9,'1_原始數據'!$I$2:$I$1000,$B9,'1_原始數據'!$C$2:$C$1000,"aw_reading")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A9,'1_原始數據'!$I$2:$I$1000,$B9,'1_原始數據'!$C$2:$C$1000,"aw_reading"))</f>
         <v/>
       </c>
@@ -9952,11 +10811,11 @@
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A10,'1_原始數據'!$I$2:$I$1000,$B10,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A10,'1_原始數據'!$I$2:$I$1000,$B10,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey"))</f>
         <v/>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="45">
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A10,'1_原始數據'!$I$2:$I$1000,$B10,'1_原始數據'!$C$2:$C$1000,"aw_reading")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A10,'1_原始數據'!$I$2:$I$1000,$B10,'1_原始數據'!$C$2:$C$1000,"aw_reading"))</f>
         <v/>
       </c>
-      <c r="L10" s="25">
+      <c r="L10" s="49">
         <f>MAX($C$5:$C$34)*1.1</f>
         <v/>
       </c>
@@ -9978,7 +10837,7 @@
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A11,'1_原始數據'!$I$2:$I$1000,$B11,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A11,'1_原始數據'!$I$2:$I$1000,$B11,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey"))</f>
         <v/>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="45">
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A11,'1_原始數據'!$I$2:$I$1000,$B11,'1_原始數據'!$C$2:$C$1000,"aw_reading")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A11,'1_原始數據'!$I$2:$I$1000,$B11,'1_原始數據'!$C$2:$C$1000,"aw_reading"))</f>
         <v/>
       </c>
@@ -10009,7 +10868,7 @@
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A12,'1_原始數據'!$I$2:$I$1000,$B12,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A12,'1_原始數據'!$I$2:$I$1000,$B12,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey"))</f>
         <v/>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="45">
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A12,'1_原始數據'!$I$2:$I$1000,$B12,'1_原始數據'!$C$2:$C$1000,"aw_reading")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A12,'1_原始數據'!$I$2:$I$1000,$B12,'1_原始數據'!$C$2:$C$1000,"aw_reading"))</f>
         <v/>
       </c>
@@ -10038,7 +10897,7 @@
           <t>aw 高於哪些下限？</t>
         </is>
       </c>
-      <c r="L12" s="25">
+      <c r="L12" s="49">
         <f>MAX($C$5:$C$34)*1.1</f>
         <v/>
       </c>
@@ -10060,7 +10919,7 @@
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A13,'1_原始數據'!$I$2:$I$1000,$B13,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A13,'1_原始數據'!$I$2:$I$1000,$B13,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey"))</f>
         <v/>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="45">
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A13,'1_原始數據'!$I$2:$I$1000,$B13,'1_原始數據'!$C$2:$C$1000,"aw_reading")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A13,'1_原始數據'!$I$2:$I$1000,$B13,'1_原始數據'!$C$2:$C$1000,"aw_reading"))</f>
         <v/>
       </c>
@@ -10073,11 +10932,11 @@
         <f>AVERAGEIF($B$5:$B$34,F13,$C$5:$C$34)</f>
         <v/>
       </c>
-      <c r="H13" s="35">
+      <c r="H13" s="51">
         <f>AVERAGEIF($B$5:$B$34,F13,$D$5:$D$34)</f>
         <v/>
       </c>
-      <c r="I13" s="14">
+      <c r="I13" s="45">
         <f t="array" ref="I13">_xlfn.STDEV.S(IF($B$5:$B$34=F13,$D$5:$D$34))</f>
         <v/>
       </c>
@@ -10099,7 +10958,7 @@
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A14,'1_原始數據'!$I$2:$I$1000,$B14,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A14,'1_原始數據'!$I$2:$I$1000,$B14,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey"))</f>
         <v/>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="45">
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A14,'1_原始數據'!$I$2:$I$1000,$B14,'1_原始數據'!$C$2:$C$1000,"aw_reading")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A14,'1_原始數據'!$I$2:$I$1000,$B14,'1_原始數據'!$C$2:$C$1000,"aw_reading"))</f>
         <v/>
       </c>
@@ -10112,11 +10971,11 @@
         <f>AVERAGEIF($B$5:$B$34,F14,$C$5:$C$34)</f>
         <v/>
       </c>
-      <c r="H14" s="35">
+      <c r="H14" s="51">
         <f>AVERAGEIF($B$5:$B$34,F14,$D$5:$D$34)</f>
         <v/>
       </c>
-      <c r="I14" s="14">
+      <c r="I14" s="45">
         <f t="array" ref="I14">_xlfn.STDEV.S(IF($B$5:$B$34=F14,$D$5:$D$34))</f>
         <v/>
       </c>
@@ -10138,7 +10997,7 @@
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A15,'1_原始數據'!$I$2:$I$1000,$B15,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A15,'1_原始數據'!$I$2:$I$1000,$B15,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey"))</f>
         <v/>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="45">
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A15,'1_原始數據'!$I$2:$I$1000,$B15,'1_原始數據'!$C$2:$C$1000,"aw_reading")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A15,'1_原始數據'!$I$2:$I$1000,$B15,'1_原始數據'!$C$2:$C$1000,"aw_reading"))</f>
         <v/>
       </c>
@@ -10151,11 +11010,11 @@
         <f>AVERAGEIF($B$5:$B$34,F15,$C$5:$C$34)</f>
         <v/>
       </c>
-      <c r="H15" s="35">
+      <c r="H15" s="51">
         <f>AVERAGEIF($B$5:$B$34,F15,$D$5:$D$34)</f>
         <v/>
       </c>
-      <c r="I15" s="14">
+      <c r="I15" s="45">
         <f t="array" ref="I15">_xlfn.STDEV.S(IF($B$5:$B$34=F15,$D$5:$D$34))</f>
         <v/>
       </c>
@@ -10177,7 +11036,7 @@
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A16,'1_原始數據'!$I$2:$I$1000,$B16,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A16,'1_原始數據'!$I$2:$I$1000,$B16,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey"))</f>
         <v/>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="45">
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A16,'1_原始數據'!$I$2:$I$1000,$B16,'1_原始數據'!$C$2:$C$1000,"aw_reading")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A16,'1_原始數據'!$I$2:$I$1000,$B16,'1_原始數據'!$C$2:$C$1000,"aw_reading"))</f>
         <v/>
       </c>
@@ -10190,11 +11049,11 @@
         <f>AVERAGEIF($B$5:$B$34,F16,$C$5:$C$34)</f>
         <v/>
       </c>
-      <c r="H16" s="35">
+      <c r="H16" s="51">
         <f>AVERAGEIF($B$5:$B$34,F16,$D$5:$D$34)</f>
         <v/>
       </c>
-      <c r="I16" s="14">
+      <c r="I16" s="45">
         <f t="array" ref="I16">_xlfn.STDEV.S(IF($B$5:$B$34=F16,$D$5:$D$34))</f>
         <v/>
       </c>
@@ -10216,7 +11075,7 @@
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A17,'1_原始數據'!$I$2:$I$1000,$B17,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A17,'1_原始數據'!$I$2:$I$1000,$B17,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey"))</f>
         <v/>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="45">
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A17,'1_原始數據'!$I$2:$I$1000,$B17,'1_原始數據'!$C$2:$C$1000,"aw_reading")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A17,'1_原始數據'!$I$2:$I$1000,$B17,'1_原始數據'!$C$2:$C$1000,"aw_reading"))</f>
         <v/>
       </c>
@@ -10229,11 +11088,11 @@
         <f>AVERAGEIF($B$5:$B$34,F17,$C$5:$C$34)</f>
         <v/>
       </c>
-      <c r="H17" s="35">
+      <c r="H17" s="51">
         <f>AVERAGEIF($B$5:$B$34,F17,$D$5:$D$34)</f>
         <v/>
       </c>
-      <c r="I17" s="14">
+      <c r="I17" s="45">
         <f t="array" ref="I17">_xlfn.STDEV.S(IF($B$5:$B$34=F17,$D$5:$D$34))</f>
         <v/>
       </c>
@@ -10255,7 +11114,7 @@
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A18,'1_原始數據'!$I$2:$I$1000,$B18,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A18,'1_原始數據'!$I$2:$I$1000,$B18,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey"))</f>
         <v/>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="45">
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A18,'1_原始數據'!$I$2:$I$1000,$B18,'1_原始數據'!$C$2:$C$1000,"aw_reading")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A18,'1_原始數據'!$I$2:$I$1000,$B18,'1_原始數據'!$C$2:$C$1000,"aw_reading"))</f>
         <v/>
       </c>
@@ -10268,11 +11127,11 @@
         <f>AVERAGEIF($B$5:$B$34,F18,$C$5:$C$34)</f>
         <v/>
       </c>
-      <c r="H18" s="35">
+      <c r="H18" s="51">
         <f>AVERAGEIF($B$5:$B$34,F18,$D$5:$D$34)</f>
         <v/>
       </c>
-      <c r="I18" s="14">
+      <c r="I18" s="45">
         <f t="array" ref="I18">_xlfn.STDEV.S(IF($B$5:$B$34=F18,$D$5:$D$34))</f>
         <v/>
       </c>
@@ -10294,7 +11153,7 @@
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A19,'1_原始數據'!$I$2:$I$1000,$B19,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A19,'1_原始數據'!$I$2:$I$1000,$B19,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey"))</f>
         <v/>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="45">
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A19,'1_原始數據'!$I$2:$I$1000,$B19,'1_原始數據'!$C$2:$C$1000,"aw_reading")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A19,'1_原始數據'!$I$2:$I$1000,$B19,'1_原始數據'!$C$2:$C$1000,"aw_reading"))</f>
         <v/>
       </c>
@@ -10317,7 +11176,7 @@
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A20,'1_原始數據'!$I$2:$I$1000,$B20,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A20,'1_原始數據'!$I$2:$I$1000,$B20,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey"))</f>
         <v/>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="45">
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A20,'1_原始數據'!$I$2:$I$1000,$B20,'1_原始數據'!$C$2:$C$1000,"aw_reading")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A20,'1_原始數據'!$I$2:$I$1000,$B20,'1_原始數據'!$C$2:$C$1000,"aw_reading"))</f>
         <v/>
       </c>
@@ -10335,7 +11194,7 @@
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A21,'1_原始數據'!$I$2:$I$1000,$B21,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A21,'1_原始數據'!$I$2:$I$1000,$B21,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey"))</f>
         <v/>
       </c>
-      <c r="D21" s="14">
+      <c r="D21" s="45">
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A21,'1_原始數據'!$I$2:$I$1000,$B21,'1_原始數據'!$C$2:$C$1000,"aw_reading")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A21,'1_原始數據'!$I$2:$I$1000,$B21,'1_原始數據'!$C$2:$C$1000,"aw_reading"))</f>
         <v/>
       </c>
@@ -10353,7 +11212,7 @@
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A22,'1_原始數據'!$I$2:$I$1000,$B22,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A22,'1_原始數據'!$I$2:$I$1000,$B22,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey"))</f>
         <v/>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="45">
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A22,'1_原始數據'!$I$2:$I$1000,$B22,'1_原始數據'!$C$2:$C$1000,"aw_reading")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A22,'1_原始數據'!$I$2:$I$1000,$B22,'1_原始數據'!$C$2:$C$1000,"aw_reading"))</f>
         <v/>
       </c>
@@ -10371,7 +11230,7 @@
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A23,'1_原始數據'!$I$2:$I$1000,$B23,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A23,'1_原始數據'!$I$2:$I$1000,$B23,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey"))</f>
         <v/>
       </c>
-      <c r="D23" s="14">
+      <c r="D23" s="45">
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A23,'1_原始數據'!$I$2:$I$1000,$B23,'1_原始數據'!$C$2:$C$1000,"aw_reading")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A23,'1_原始數據'!$I$2:$I$1000,$B23,'1_原始數據'!$C$2:$C$1000,"aw_reading"))</f>
         <v/>
       </c>
@@ -10389,7 +11248,7 @@
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A24,'1_原始數據'!$I$2:$I$1000,$B24,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A24,'1_原始數據'!$I$2:$I$1000,$B24,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey"))</f>
         <v/>
       </c>
-      <c r="D24" s="14">
+      <c r="D24" s="45">
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A24,'1_原始數據'!$I$2:$I$1000,$B24,'1_原始數據'!$C$2:$C$1000,"aw_reading")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A24,'1_原始數據'!$I$2:$I$1000,$B24,'1_原始數據'!$C$2:$C$1000,"aw_reading"))</f>
         <v/>
       </c>
@@ -10407,7 +11266,7 @@
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A25,'1_原始數據'!$I$2:$I$1000,$B25,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A25,'1_原始數據'!$I$2:$I$1000,$B25,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey"))</f>
         <v/>
       </c>
-      <c r="D25" s="14">
+      <c r="D25" s="45">
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A25,'1_原始數據'!$I$2:$I$1000,$B25,'1_原始數據'!$C$2:$C$1000,"aw_reading")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A25,'1_原始數據'!$I$2:$I$1000,$B25,'1_原始數據'!$C$2:$C$1000,"aw_reading"))</f>
         <v/>
       </c>
@@ -10425,7 +11284,7 @@
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A26,'1_原始數據'!$I$2:$I$1000,$B26,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A26,'1_原始數據'!$I$2:$I$1000,$B26,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey"))</f>
         <v/>
       </c>
-      <c r="D26" s="14">
+      <c r="D26" s="45">
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A26,'1_原始數據'!$I$2:$I$1000,$B26,'1_原始數據'!$C$2:$C$1000,"aw_reading")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A26,'1_原始數據'!$I$2:$I$1000,$B26,'1_原始數據'!$C$2:$C$1000,"aw_reading"))</f>
         <v/>
       </c>
@@ -10443,7 +11302,7 @@
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A27,'1_原始數據'!$I$2:$I$1000,$B27,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A27,'1_原始數據'!$I$2:$I$1000,$B27,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey"))</f>
         <v/>
       </c>
-      <c r="D27" s="14">
+      <c r="D27" s="45">
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A27,'1_原始數據'!$I$2:$I$1000,$B27,'1_原始數據'!$C$2:$C$1000,"aw_reading")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A27,'1_原始數據'!$I$2:$I$1000,$B27,'1_原始數據'!$C$2:$C$1000,"aw_reading"))</f>
         <v/>
       </c>
@@ -10461,7 +11320,7 @@
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A28,'1_原始數據'!$I$2:$I$1000,$B28,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A28,'1_原始數據'!$I$2:$I$1000,$B28,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey"))</f>
         <v/>
       </c>
-      <c r="D28" s="14">
+      <c r="D28" s="45">
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A28,'1_原始數據'!$I$2:$I$1000,$B28,'1_原始數據'!$C$2:$C$1000,"aw_reading")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A28,'1_原始數據'!$I$2:$I$1000,$B28,'1_原始數據'!$C$2:$C$1000,"aw_reading"))</f>
         <v/>
       </c>
@@ -10479,7 +11338,7 @@
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A29,'1_原始數據'!$I$2:$I$1000,$B29,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A29,'1_原始數據'!$I$2:$I$1000,$B29,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey"))</f>
         <v/>
       </c>
-      <c r="D29" s="14">
+      <c r="D29" s="45">
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A29,'1_原始數據'!$I$2:$I$1000,$B29,'1_原始數據'!$C$2:$C$1000,"aw_reading")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A29,'1_原始數據'!$I$2:$I$1000,$B29,'1_原始數據'!$C$2:$C$1000,"aw_reading"))</f>
         <v/>
       </c>
@@ -10497,7 +11356,7 @@
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A30,'1_原始數據'!$I$2:$I$1000,$B30,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A30,'1_原始數據'!$I$2:$I$1000,$B30,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey"))</f>
         <v/>
       </c>
-      <c r="D30" s="14">
+      <c r="D30" s="45">
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A30,'1_原始數據'!$I$2:$I$1000,$B30,'1_原始數據'!$C$2:$C$1000,"aw_reading")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A30,'1_原始數據'!$I$2:$I$1000,$B30,'1_原始數據'!$C$2:$C$1000,"aw_reading"))</f>
         <v/>
       </c>
@@ -10515,7 +11374,7 @@
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A31,'1_原始數據'!$I$2:$I$1000,$B31,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A31,'1_原始數據'!$I$2:$I$1000,$B31,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey"))</f>
         <v/>
       </c>
-      <c r="D31" s="14">
+      <c r="D31" s="45">
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A31,'1_原始數據'!$I$2:$I$1000,$B31,'1_原始數據'!$C$2:$C$1000,"aw_reading")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A31,'1_原始數據'!$I$2:$I$1000,$B31,'1_原始數據'!$C$2:$C$1000,"aw_reading"))</f>
         <v/>
       </c>
@@ -10533,7 +11392,7 @@
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A32,'1_原始數據'!$I$2:$I$1000,$B32,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A32,'1_原始數據'!$I$2:$I$1000,$B32,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey"))</f>
         <v/>
       </c>
-      <c r="D32" s="14">
+      <c r="D32" s="45">
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A32,'1_原始數據'!$I$2:$I$1000,$B32,'1_原始數據'!$C$2:$C$1000,"aw_reading")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A32,'1_原始數據'!$I$2:$I$1000,$B32,'1_原始數據'!$C$2:$C$1000,"aw_reading"))</f>
         <v/>
       </c>
@@ -10551,7 +11410,7 @@
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A33,'1_原始數據'!$I$2:$I$1000,$B33,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A33,'1_原始數據'!$I$2:$I$1000,$B33,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey"))</f>
         <v/>
       </c>
-      <c r="D33" s="14">
+      <c r="D33" s="45">
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A33,'1_原始數據'!$I$2:$I$1000,$B33,'1_原始數據'!$C$2:$C$1000,"aw_reading")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A33,'1_原始數據'!$I$2:$I$1000,$B33,'1_原始數據'!$C$2:$C$1000,"aw_reading"))</f>
         <v/>
       </c>
@@ -10569,7 +11428,7 @@
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A34,'1_原始數據'!$I$2:$I$1000,$B34,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A34,'1_原始數據'!$I$2:$I$1000,$B34,'1_原始數據'!$C$2:$C$1000,"moisture_pct_survey"))</f>
         <v/>
       </c>
-      <c r="D34" s="14">
+      <c r="D34" s="45">
         <f>IF(COUNTIFS('1_原始數據'!$A$2:$A$1000,$A34,'1_原始數據'!$I$2:$I$1000,$B34,'1_原始數據'!$C$2:$C$1000,"aw_reading")=0,"",SUMIFS('1_原始數據'!$E$2:$E$1000,'1_原始數據'!$A$2:$A$1000,$A34,'1_原始數據'!$I$2:$I$1000,$B34,'1_原始數據'!$C$2:$C$1000,"aw_reading"))</f>
         <v/>
       </c>
@@ -10590,10 +11449,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A35:D35"/>
     <mergeCell ref="F19:J20"/>
-    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="F47:M47"/>
     <mergeCell ref="A2:M2"/>
-    <mergeCell ref="F47:M47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -10744,7 +11603,7 @@
           <t>RSD (%)</t>
         </is>
       </c>
-      <c r="B15" s="40">
+      <c r="B15" s="52">
         <f>B14/B13*100</f>
         <v/>
       </c>
@@ -10782,128 +11641,2515 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00B3306A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B25"/>
+  <dimension ref="A1:T69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="3" customWidth="1" min="12" max="12"/>
+    <col width="36" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="3" customWidth="1" min="17" max="17"/>
+    <col width="3" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>練習題（寫在黃色格子裡，交報告時一起附上）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="48" customHeight="1">
-      <c r="B3" s="41" t="inlineStr">
-        <is>
-          <t>問題 1：牛肉乾質量平衡：工廠影片聲稱「500 g 鮮肉 → 100 g 牛肉乾」。瘦牛肉約 73% 水分，成品約 20% 水分，加工中固形物幾乎不流失。(1) 用質量平衡算合理的產率 (%) 與成品克數；(2) 跟影片的 100 g 差多少？(3) 若真的只得 100 g（20% 水分），還能同時支持影片「&gt; 30 g 蛋白質／100 g」的說法嗎？</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="B4" s="18" t="inlineStr">
-        <is>
-          <t>提示：在任一空白格自己打公式：固形物 = 500 × (1 − 0.73)；成品重 = 固形物 ÷ (1 − 0.20)；產率 = 成品重 ÷ 500 × 100。第 (3) 小題：先算 100 g 成品裡「該有」多少固形物，再和 500 g 鮮肉實際有多少固形物比較。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="B5" s="42" t="inlineStr"/>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="B7" s="41" t="inlineStr">
-        <is>
-          <t>問題 2：濕基／乾基練習：空盤 22.3300 g；盤+樣品 26.3300 g；乾燥後 25.5300 g。算出濕基 % 與乾基 %，並說明兩個數字為什麼不一樣。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>提示：把「2_濕基乾基」C9–C11 改成這三個數字，讀 C15、C16。做完記得改回 25.1234／28.1234／27.9734。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="B9" s="42" t="inlineStr"/>
-    </row>
-    <row r="11" ht="48" customHeight="1">
-      <c r="B11" s="41" t="inlineStr">
-        <is>
-          <t>問題 3：恆重判斷：連續三次乾燥後秤重 12.4050 g → 12.3890 g → 12.3860 g。(1) 第 3 次秤重後達到恆重了嗎？(2) 如果還沒，下一步該做什麼？(3) 再烘一次後第 4 次秤得 12.3851 g，現在恆重了嗎？該用哪一個重量算水分？</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>提示：把「2_濕基乾基」C23–C25 改成這三個數字，看 C28 的判定。第 (3) 小題：把 C23–C25 改成第 2、3、4 次的重量（12.3890、12.3860、12.3851）再看一次判定。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="B13" s="42" t="inlineStr"/>
-    </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="B15" s="41" t="inlineStr">
-        <is>
-          <t>問題 4：比較「4_各組統計」各食品的 RSD%，哪一種食品精密度看起來最差？可能是操作的原因，還是樣品本身的原因？</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>提示：看 D11 的答案，再比較該食品的 SD（E 欄）是否真的比別的食品大。RSD = SD ÷ 平均，平均很小時 RSD 會被放大。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="B17" s="42" t="inlineStr"/>
-    </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="B19" s="41" t="inlineStr">
-        <is>
-          <t>問題 5：牛肉乾與龍眼乾水分都約 20%，但 aw 不同。哪一個比較容易發黴？請用「6_水活性」的微生物下限說明。</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>提示：看 H、J 欄的平均 aw 與判定，並對照下面的散佈圖。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="B21" s="42" t="inlineStr"/>
-    </row>
-    <row r="23" ht="32" customHeight="1">
-      <c r="B23" s="41" t="inlineStr">
-        <is>
-          <t>問題 6：「5_烘箱vs紅外線」為什麼要用「成對」t 檢定，而不是把烘箱法 15 個值和紅外線 15 個值當成兩組獨立數據比較？試試看把 T.TEST 的最後一個參數從 1（成對）改成 2（兩組獨立、等變異），p 值怎麼變？為什麼？</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>提示：在 J12 旁邊的空白格打 =T.TEST(E5:E19,D5:D19,2,2)。提示：15 份樣品的水分從 1% 到 35%，兩組各自的 SD 很大。</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="B25" s="42" t="inlineStr"/>
-    </row>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>步驟 8（延伸）　等溫吸濕曲線：麵條真實數據算得出單分子層水嗎？</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="48" customHeight="1">
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t>真實數據：麵條在 28 °C 乾燥過程中的 8 個取樣點，同一份樣品以 105 °C 烘箱法與 FD-660 紅外線水分計測水分（濕基 %），並以 aw 計測水活性（data/w02_noodle_msi.csv）。等溫吸濕曲線 (MSI) 的 y 軸用乾基 X = 濕基% ÷ (100 − 濕基%)。教科書說用 BET 或 GAB 擬合就能算出單分子層水 Xm；這張表要練習判斷：算出來的 Xm，數據撐得住嗎？互動版：https://tai-shengyeh.github.io/food-analysis-lab/labs/w02_moisture/isotherm.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>① 原始數據與換算（黃色可換成你自己的 8 個點）</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>② BET 線性化</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>圖用輔助數據（自動計算）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>取樣時間</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>aw</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>烘箱 水分 (%wb)</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>FD-660 水分 (%wb)</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>烘箱 X (g/g)</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>FD-660 X (g/g)</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>分析用 X (g/g)</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>BET：aw/[(1−aw)X]</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>GAB：aw/X</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>aw²</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>aw</t>
+        </is>
+      </c>
+      <c r="M4" s="21" t="inlineStr">
+        <is>
+          <t>分析用的水分數據</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>烘箱法</t>
+        </is>
+      </c>
+      <c r="S4" s="9" t="inlineStr">
+        <is>
+          <t>aw</t>
+        </is>
+      </c>
+      <c r="T4" s="9" t="inlineStr">
+        <is>
+          <t>X_GAB（⑤）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="53" t="inlineStr">
+        <is>
+          <t>1425</t>
+        </is>
+      </c>
+      <c r="B5" s="54" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="C5" s="39" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="D5" s="39" t="n">
+        <v>16.81</v>
+      </c>
+      <c r="E5" s="55">
+        <f>C5/(100-C5)</f>
+        <v/>
+      </c>
+      <c r="F5" s="55">
+        <f>D5/(100-D5)</f>
+        <v/>
+      </c>
+      <c r="G5" s="55">
+        <f>IF($N$4="FD-660",F5,E5)</f>
+        <v/>
+      </c>
+      <c r="H5" s="56">
+        <f>B5/((1-B5)*G5)</f>
+        <v/>
+      </c>
+      <c r="I5" s="57">
+        <f>B5/G5</f>
+        <v/>
+      </c>
+      <c r="J5" s="55">
+        <f>B5^2</f>
+        <v/>
+      </c>
+      <c r="K5" s="57">
+        <f>B5</f>
+        <v/>
+      </c>
+      <c r="M5" s="21" t="inlineStr">
+        <is>
+          <t>BET 適用範圍上限 aw</t>
+        </is>
+      </c>
+      <c r="N5" s="58" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="S5" s="59">
+        <f>0.05</f>
+        <v/>
+      </c>
+      <c r="T5" s="60">
+        <f>N$41*N$42*N$43*S5/((1-N$43*S5)*(1-N$43*S5+N$42*N$43*S5))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="53" t="inlineStr">
+        <is>
+          <t>1455</t>
+        </is>
+      </c>
+      <c r="B6" s="54" t="n">
+        <v>0.856</v>
+      </c>
+      <c r="C6" s="39" t="n">
+        <v>17.55</v>
+      </c>
+      <c r="D6" s="39" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="E6" s="55">
+        <f>C6/(100-C6)</f>
+        <v/>
+      </c>
+      <c r="F6" s="55">
+        <f>D6/(100-D6)</f>
+        <v/>
+      </c>
+      <c r="G6" s="55">
+        <f>IF($N$4="FD-660",F6,E6)</f>
+        <v/>
+      </c>
+      <c r="H6" s="56">
+        <f>B6/((1-B6)*G6)</f>
+        <v/>
+      </c>
+      <c r="I6" s="57">
+        <f>B6/G6</f>
+        <v/>
+      </c>
+      <c r="J6" s="55">
+        <f>B6^2</f>
+        <v/>
+      </c>
+      <c r="K6" s="57">
+        <f>B6</f>
+        <v/>
+      </c>
+      <c r="M6" s="21" t="inlineStr">
+        <is>
+          <t>範圍內（0.05 ≤ aw ≤ 上限）的點數</t>
+        </is>
+      </c>
+      <c r="N6" s="61">
+        <f>COUNTIFS(B5:B12,"&gt;=0.05",B5:B12,"&lt;="&amp;N5)</f>
+        <v/>
+      </c>
+      <c r="S6" s="59">
+        <f>0.10</f>
+        <v/>
+      </c>
+      <c r="T6" s="60">
+        <f>N$41*N$42*N$43*S6/((1-N$43*S6)*(1-N$43*S6+N$42*N$43*S6))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="53" t="inlineStr">
+        <is>
+          <t>1525</t>
+        </is>
+      </c>
+      <c r="B7" s="54" t="n">
+        <v>0.866</v>
+      </c>
+      <c r="C7" s="39" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="D7" s="39" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="E7" s="55">
+        <f>C7/(100-C7)</f>
+        <v/>
+      </c>
+      <c r="F7" s="55">
+        <f>D7/(100-D7)</f>
+        <v/>
+      </c>
+      <c r="G7" s="55">
+        <f>IF($N$4="FD-660",F7,E7)</f>
+        <v/>
+      </c>
+      <c r="H7" s="56">
+        <f>B7/((1-B7)*G7)</f>
+        <v/>
+      </c>
+      <c r="I7" s="57">
+        <f>B7/G7</f>
+        <v/>
+      </c>
+      <c r="J7" s="55">
+        <f>B7^2</f>
+        <v/>
+      </c>
+      <c r="K7" s="57">
+        <f>B7</f>
+        <v/>
+      </c>
+      <c r="M7" s="21" t="inlineStr">
+        <is>
+          <t>斜率 s（硬套全部 8 點）</t>
+        </is>
+      </c>
+      <c r="N7" s="56">
+        <f>SLOPE(H5:H12,B5:B12)</f>
+        <v/>
+      </c>
+      <c r="S7" s="59">
+        <f>0.15</f>
+        <v/>
+      </c>
+      <c r="T7" s="60">
+        <f>N$41*N$42*N$43*S7/((1-N$43*S7)*(1-N$43*S7+N$42*N$43*S7))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="53" t="inlineStr">
+        <is>
+          <t>1555</t>
+        </is>
+      </c>
+      <c r="B8" s="54" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="C8" s="39" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="D8" s="39" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="E8" s="55">
+        <f>C8/(100-C8)</f>
+        <v/>
+      </c>
+      <c r="F8" s="55">
+        <f>D8/(100-D8)</f>
+        <v/>
+      </c>
+      <c r="G8" s="55">
+        <f>IF($N$4="FD-660",F8,E8)</f>
+        <v/>
+      </c>
+      <c r="H8" s="56">
+        <f>B8/((1-B8)*G8)</f>
+        <v/>
+      </c>
+      <c r="I8" s="57">
+        <f>B8/G8</f>
+        <v/>
+      </c>
+      <c r="J8" s="55">
+        <f>B8^2</f>
+        <v/>
+      </c>
+      <c r="K8" s="57">
+        <f>B8</f>
+        <v/>
+      </c>
+      <c r="M8" s="21" t="inlineStr">
+        <is>
+          <t>截距 i</t>
+        </is>
+      </c>
+      <c r="N8" s="56">
+        <f>INTERCEPT(H5:H12,B5:B12)</f>
+        <v/>
+      </c>
+      <c r="S8" s="59">
+        <f>0.20</f>
+        <v/>
+      </c>
+      <c r="T8" s="60">
+        <f>N$41*N$42*N$43*S8/((1-N$43*S8)*(1-N$43*S8+N$42*N$43*S8))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="53" t="inlineStr">
+        <is>
+          <t>1625</t>
+        </is>
+      </c>
+      <c r="B9" s="54" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="C9" s="39" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="D9" s="39" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="E9" s="55">
+        <f>C9/(100-C9)</f>
+        <v/>
+      </c>
+      <c r="F9" s="55">
+        <f>D9/(100-D9)</f>
+        <v/>
+      </c>
+      <c r="G9" s="55">
+        <f>IF($N$4="FD-660",F9,E9)</f>
+        <v/>
+      </c>
+      <c r="H9" s="56">
+        <f>B9/((1-B9)*G9)</f>
+        <v/>
+      </c>
+      <c r="I9" s="57">
+        <f>B9/G9</f>
+        <v/>
+      </c>
+      <c r="J9" s="55">
+        <f>B9^2</f>
+        <v/>
+      </c>
+      <c r="K9" s="57">
+        <f>B9</f>
+        <v/>
+      </c>
+      <c r="M9" s="21" t="inlineStr">
+        <is>
+          <t>R²</t>
+        </is>
+      </c>
+      <c r="N9" s="57">
+        <f>RSQ(H5:H12,B5:B12)</f>
+        <v/>
+      </c>
+      <c r="S9" s="59">
+        <f>0.25</f>
+        <v/>
+      </c>
+      <c r="T9" s="60">
+        <f>N$41*N$42*N$43*S9/((1-N$43*S9)*(1-N$43*S9+N$42*N$43*S9))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="53" t="inlineStr">
+        <is>
+          <t>1655</t>
+        </is>
+      </c>
+      <c r="B10" s="54" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="C10" s="39" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="D10" s="39" t="n">
+        <v>10.07</v>
+      </c>
+      <c r="E10" s="55">
+        <f>C10/(100-C10)</f>
+        <v/>
+      </c>
+      <c r="F10" s="55">
+        <f>D10/(100-D10)</f>
+        <v/>
+      </c>
+      <c r="G10" s="55">
+        <f>IF($N$4="FD-660",F10,E10)</f>
+        <v/>
+      </c>
+      <c r="H10" s="56">
+        <f>B10/((1-B10)*G10)</f>
+        <v/>
+      </c>
+      <c r="I10" s="57">
+        <f>B10/G10</f>
+        <v/>
+      </c>
+      <c r="J10" s="55">
+        <f>B10^2</f>
+        <v/>
+      </c>
+      <c r="K10" s="57">
+        <f>B10</f>
+        <v/>
+      </c>
+      <c r="M10" s="21" t="inlineStr">
+        <is>
+          <t>C = 1 + s/i</t>
+        </is>
+      </c>
+      <c r="N10" s="62">
+        <f>1+N7/N8</f>
+        <v/>
+      </c>
+      <c r="S10" s="59">
+        <f>0.30</f>
+        <v/>
+      </c>
+      <c r="T10" s="60">
+        <f>N$41*N$42*N$43*S10/((1-N$43*S10)*(1-N$43*S10+N$42*N$43*S10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="53" t="inlineStr">
+        <is>
+          <t>1755</t>
+        </is>
+      </c>
+      <c r="B11" s="54" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="C11" s="39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="D11" s="39" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="E11" s="55">
+        <f>C11/(100-C11)</f>
+        <v/>
+      </c>
+      <c r="F11" s="55">
+        <f>D11/(100-D11)</f>
+        <v/>
+      </c>
+      <c r="G11" s="55">
+        <f>IF($N$4="FD-660",F11,E11)</f>
+        <v/>
+      </c>
+      <c r="H11" s="56">
+        <f>B11/((1-B11)*G11)</f>
+        <v/>
+      </c>
+      <c r="I11" s="57">
+        <f>B11/G11</f>
+        <v/>
+      </c>
+      <c r="J11" s="55">
+        <f>B11^2</f>
+        <v/>
+      </c>
+      <c r="K11" s="57">
+        <f>B11</f>
+        <v/>
+      </c>
+      <c r="M11" s="21" t="inlineStr">
+        <is>
+          <t>Xm = 1/(s + i)  (g/g)</t>
+        </is>
+      </c>
+      <c r="N11" s="63">
+        <f>1/(N7+N8)</f>
+        <v/>
+      </c>
+      <c r="S11" s="59">
+        <f>0.35</f>
+        <v/>
+      </c>
+      <c r="T11" s="60">
+        <f>N$41*N$42*N$43*S11/((1-N$43*S11)*(1-N$43*S11+N$42*N$43*S11))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="53" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="B12" s="54" t="n">
+        <v>0.5580000000000001</v>
+      </c>
+      <c r="C12" s="39" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="D12" s="39" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="E12" s="55">
+        <f>C12/(100-C12)</f>
+        <v/>
+      </c>
+      <c r="F12" s="55">
+        <f>D12/(100-D12)</f>
+        <v/>
+      </c>
+      <c r="G12" s="55">
+        <f>IF($N$4="FD-660",F12,E12)</f>
+        <v/>
+      </c>
+      <c r="H12" s="56">
+        <f>B12/((1-B12)*G12)</f>
+        <v/>
+      </c>
+      <c r="I12" s="57">
+        <f>B12/G12</f>
+        <v/>
+      </c>
+      <c r="J12" s="55">
+        <f>B12^2</f>
+        <v/>
+      </c>
+      <c r="K12" s="57">
+        <f>B12</f>
+        <v/>
+      </c>
+      <c r="M12" s="21" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="N12" s="7">
+        <f>IF(N6&lt;3,"✘ 範圍內不足 3 點，不能用",IF(N10&lt;=0,"✘ C ≤ 0，不合理","✔ 參數合理"))</f>
+        <v/>
+      </c>
+      <c r="S12" s="59">
+        <f>0.40</f>
+        <v/>
+      </c>
+      <c r="T12" s="60">
+        <f>N$41*N$42*N$43*S12/((1-N$43*S12)*(1-N$43*S12+N$42*N$43*S12))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>8 列都要填滿（LINEST 不接受空格）。烘箱 − FD-660 平均差約 0.7 %wb：兩種方法會給出兩條不同的曲線，報告時要註明用哪一種。分析用 X 由 N4 選擇；④ 輪廓表固定用烘箱法。</t>
+        </is>
+      </c>
+      <c r="M13" s="18" t="inlineStr">
+        <is>
+          <t>BET：aw/[(1−aw)X] = 1/(XmC) + [(C−1)/(XmC)]·aw。C 與吸附熱有關，必須 &gt; 0。R² 很高只代表點排得直，不代表模型在這段 aw 成立——先檢查範圍！</t>
+        </is>
+      </c>
+      <c r="S13" s="59">
+        <f>0.45</f>
+        <v/>
+      </c>
+      <c r="T13" s="60">
+        <f>N$41*N$42*N$43*S13/((1-N$43*S13)*(1-N$43*S13+N$42*N$43*S13))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="S14" s="59">
+        <f>0.50</f>
+        <v/>
+      </c>
+      <c r="T14" s="60">
+        <f>N$41*N$42*N$43*S14/((1-N$43*S14)*(1-N$43*S14+N$42*N$43*S14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>④ GAB 輪廓：把 Xm 固定，看誤差差多少（烘箱法數據）</t>
+        </is>
+      </c>
+      <c r="S15" s="59">
+        <f>0.55</f>
+        <v/>
+      </c>
+      <c r="T15" s="60">
+        <f>N$41*N$42*N$43*S15/((1-N$43*S15)*(1-N$43*S15+N$42*N$43*S15))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>C、K 是 Colab（NB02 第 7.3 節，scipy curve_fit）在每個固定 Xm 下找到的最佳值，直接貼在這裡（灰字）；SSE、Δ 由 Excel 公式算。Δ = (SSE − SSE最小) ÷ σ²；Δ ≤ 3.84 代表這個 Xm 和最佳值的差異可以用量測誤差解釋，數據無法排除它（95%）。換了 ① 的數據，C、K 要重算（用 ⑤ 的規劃求解或 Colab）。</t>
+        </is>
+      </c>
+      <c r="S16" s="59">
+        <f>0.60</f>
+        <v/>
+      </c>
+      <c r="T16" s="60">
+        <f>N$41*N$42*N$43*S16/((1-N$43*S16)*(1-N$43*S16+N$42*N$43*S16))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>③ GAB 二次式線性化：aw/X = α·aw² + β·aw + γ</t>
+        </is>
+      </c>
+      <c r="S17" s="59">
+        <f>0.65</f>
+        <v/>
+      </c>
+      <c r="T17" s="60">
+        <f>N$41*N$42*N$43*S17/((1-N$43*S17)*(1-N$43*S17+N$42*N$43*S17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="M18" s="21" t="inlineStr">
+        <is>
+          <t>α（LINEST）</t>
+        </is>
+      </c>
+      <c r="N18" s="57">
+        <f>INDEX(LINEST($I$5:$I$12,$J$5:$K$12),1,2)</f>
+        <v/>
+      </c>
+      <c r="S18" s="59">
+        <f>0.70</f>
+        <v/>
+      </c>
+      <c r="T18" s="60">
+        <f>N$41*N$42*N$43*S18/((1-N$43*S18)*(1-N$43*S18+N$42*N$43*S18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>固定 Xm</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>C（Colab）</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>K（Colab）</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>SSE</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>RMSE (g/g)</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>Δ</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="M19" s="21" t="inlineStr">
+        <is>
+          <t>β</t>
+        </is>
+      </c>
+      <c r="N19" s="57">
+        <f>INDEX(LINEST($I$5:$I$12,$J$5:$K$12),1,1)</f>
+        <v/>
+      </c>
+      <c r="S19" s="59">
+        <f>0.75</f>
+        <v/>
+      </c>
+      <c r="T19" s="60">
+        <f>N$41*N$42*N$43*S19/((1-N$43*S19)*(1-N$43*S19+N$42*N$43*S19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="44" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="B20" s="64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C20" s="65" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="D20" s="66">
+        <f>SUMPRODUCT((A20*B20*C20*$B$5:$B$12/((1-C20*$B$5:$B$12)*(1-C20*$B$5:$B$12+B20*C20*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E20" s="55">
+        <f>SQRT(D20/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F20" s="56">
+        <f>(D20-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G20" s="67">
+        <f>IF(F20&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+      <c r="M20" s="21" t="inlineStr">
+        <is>
+          <t>γ（物理上必須 &gt; 0）</t>
+        </is>
+      </c>
+      <c r="N20" s="57">
+        <f>INDEX(LINEST($I$5:$I$12,$J$5:$K$12),1,3)</f>
+        <v/>
+      </c>
+      <c r="S20" s="59">
+        <f>0.80</f>
+        <v/>
+      </c>
+      <c r="T20" s="60">
+        <f>N$41*N$42*N$43*S20/((1-N$43*S20)*(1-N$43*S20+N$42*N$43*S20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="44" t="n">
+        <v>0.0325</v>
+      </c>
+      <c r="B21" s="64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C21" s="65" t="n">
+        <v>0.98956</v>
+      </c>
+      <c r="D21" s="66">
+        <f>SUMPRODUCT((A21*B21*C21*$B$5:$B$12/((1-C21*$B$5:$B$12)*(1-C21*$B$5:$B$12+B21*C21*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E21" s="55">
+        <f>SQRT(D21/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F21" s="56">
+        <f>(D21-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G21" s="67">
+        <f>IF(F21&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+      <c r="M21" s="21" t="inlineStr">
+        <is>
+          <t>K = [√(β² − 4αγ) − β] / (2γ)</t>
+        </is>
+      </c>
+      <c r="N21" s="57">
+        <f>IFERROR((SQRT(N19^2-4*N18*N20)-N19)/(2*N20),"無解")</f>
+        <v/>
+      </c>
+      <c r="S21" s="59">
+        <f>0.85</f>
+        <v/>
+      </c>
+      <c r="T21" s="60">
+        <f>N$41*N$42*N$43*S21/((1-N$43*S21)*(1-N$43*S21+N$42*N$43*S21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="44" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="B22" s="64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C22" s="65" t="n">
+        <v>0.97638</v>
+      </c>
+      <c r="D22" s="66">
+        <f>SUMPRODUCT((A22*B22*C22*$B$5:$B$12/((1-C22*$B$5:$B$12)*(1-C22*$B$5:$B$12+B22*C22*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E22" s="55">
+        <f>SQRT(D22/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F22" s="56">
+        <f>(D22-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G22" s="67">
+        <f>IF(F22&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+      <c r="M22" s="21" t="inlineStr">
+        <is>
+          <t>Xm = 1/(β + 2Kγ)  (g/g)</t>
+        </is>
+      </c>
+      <c r="N22" s="63">
+        <f>IFERROR(1/(N19+2*N21*N20),"無解")</f>
+        <v/>
+      </c>
+      <c r="S22" s="59">
+        <f>0.90</f>
+        <v/>
+      </c>
+      <c r="T22" s="60">
+        <f>N$41*N$42*N$43*S22/((1-N$43*S22)*(1-N$43*S22+N$42*N$43*S22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="44" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="B23" s="64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C23" s="65" t="n">
+        <v>0.96304</v>
+      </c>
+      <c r="D23" s="66">
+        <f>SUMPRODUCT((A23*B23*C23*$B$5:$B$12/((1-C23*$B$5:$B$12)*(1-C23*$B$5:$B$12+B23*C23*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E23" s="55">
+        <f>SQRT(D23/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F23" s="56">
+        <f>(D23-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G23" s="67">
+        <f>IF(F23&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+      <c r="M23" s="21" t="inlineStr">
+        <is>
+          <t>C = β/(γK) + 2</t>
+        </is>
+      </c>
+      <c r="N23" s="62">
+        <f>IFERROR(N19/(N20*N21)+2,"無解")</f>
+        <v/>
+      </c>
+      <c r="S23" s="59">
+        <f>0.95</f>
+        <v/>
+      </c>
+      <c r="T23" s="60">
+        <f>N$41*N$42*N$43*S23/((1-N$43*S23)*(1-N$43*S23+N$42*N$43*S23))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="44" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="B24" s="64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C24" s="65" t="n">
+        <v>0.94953</v>
+      </c>
+      <c r="D24" s="66">
+        <f>SUMPRODUCT((A24*B24*C24*$B$5:$B$12/((1-C24*$B$5:$B$12)*(1-C24*$B$5:$B$12+B24*C24*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E24" s="55">
+        <f>SQRT(D24/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F24" s="56">
+        <f>(D24-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G24" s="67">
+        <f>IF(F24&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+      <c r="M24" s="21" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="N24" s="7">
+        <f>IF(N20&lt;=0,"✘ γ ≤ 0 ⇒ C &lt; 0，不合理",IF(OR(N21&lt;=0,N21&gt;=1,N23&lt;=0),"✘ 參數不合理","✔ 參數合理"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="44" t="n">
+        <v>0.0425</v>
+      </c>
+      <c r="B25" s="64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C25" s="65" t="n">
+        <v>0.93582</v>
+      </c>
+      <c r="D25" s="66">
+        <f>SUMPRODUCT((A25*B25*C25*$B$5:$B$12/((1-C25*$B$5:$B$12)*(1-C25*$B$5:$B$12+B25*C25*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E25" s="55">
+        <f>SQRT(D25/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F25" s="56">
+        <f>(D25-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G25" s="67">
+        <f>IF(F25&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+      <c r="M25" s="18" t="inlineStr">
+        <is>
+          <t>GAB：X = Xm·C·K·aw / [(1 − K·aw)(1 − K·aw + C·K·aw)]。整理成二次式後，Excel 用 LINEST 就能擬合；但 γ = 1/(Xm·C·K)，γ &lt; 0 就代表 C 是負的。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="44" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="B26" s="64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C26" s="65" t="n">
+        <v>0.92192</v>
+      </c>
+      <c r="D26" s="66">
+        <f>SUMPRODUCT((A26*B26*C26*$B$5:$B$12/((1-C26*$B$5:$B$12)*(1-C26*$B$5:$B$12+B26*C26*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E26" s="55">
+        <f>SQRT(D26/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F26" s="56">
+        <f>(D26-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G26" s="67">
+        <f>IF(F26&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+      <c r="S26" s="9" t="inlineStr">
+        <is>
+          <t>Xm</t>
+        </is>
+      </c>
+      <c r="T26" s="9" t="inlineStr">
+        <is>
+          <t>3.84</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="44" t="n">
+        <v>0.0475</v>
+      </c>
+      <c r="B27" s="64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C27" s="65" t="n">
+        <v>0.9078000000000001</v>
+      </c>
+      <c r="D27" s="66">
+        <f>SUMPRODUCT((A27*B27*C27*$B$5:$B$12/((1-C27*$B$5:$B$12)*(1-C27*$B$5:$B$12+B27*C27*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E27" s="55">
+        <f>SQRT(D27/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F27" s="56">
+        <f>(D27-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G27" s="67">
+        <f>IF(F27&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+      <c r="S27" s="68">
+        <f>A20</f>
+        <v/>
+      </c>
+      <c r="T27" s="59" t="n">
+        <v>3.84</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="44" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="B28" s="64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C28" s="65" t="n">
+        <v>0.89347</v>
+      </c>
+      <c r="D28" s="66">
+        <f>SUMPRODUCT((A28*B28*C28*$B$5:$B$12/((1-C28*$B$5:$B$12)*(1-C28*$B$5:$B$12+B28*C28*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E28" s="55">
+        <f>SQRT(D28/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F28" s="56">
+        <f>(D28-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G28" s="67">
+        <f>IF(F28&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+      <c r="S28" s="68">
+        <f>A68</f>
+        <v/>
+      </c>
+      <c r="T28" s="59" t="n">
+        <v>3.84</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="44" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="B29" s="64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C29" s="65" t="n">
+        <v>0.8789</v>
+      </c>
+      <c r="D29" s="66">
+        <f>SUMPRODUCT((A29*B29*C29*$B$5:$B$12/((1-C29*$B$5:$B$12)*(1-C29*$B$5:$B$12+B29*C29*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E29" s="55">
+        <f>SQRT(D29/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F29" s="56">
+        <f>(D29-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G29" s="67">
+        <f>IF(F29&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>④ 輪廓結果</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="44" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="B30" s="64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C30" s="65" t="n">
+        <v>0.8641</v>
+      </c>
+      <c r="D30" s="66">
+        <f>SUMPRODUCT((A30*B30*C30*$B$5:$B$12/((1-C30*$B$5:$B$12)*(1-C30*$B$5:$B$12+B30*C30*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E30" s="55">
+        <f>SQRT(D30/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F30" s="56">
+        <f>(D30-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G30" s="67">
+        <f>IF(F30&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+      <c r="M30" s="21" t="inlineStr">
+        <is>
+          <t>每點量測誤差 σ (g/g)</t>
+        </is>
+      </c>
+      <c r="N30" s="69" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="44" t="n">
+        <v>0.0575</v>
+      </c>
+      <c r="B31" s="64" t="n">
+        <v>86.786</v>
+      </c>
+      <c r="C31" s="65" t="n">
+        <v>0.85071</v>
+      </c>
+      <c r="D31" s="66">
+        <f>SUMPRODUCT((A31*B31*C31*$B$5:$B$12/((1-C31*$B$5:$B$12)*(1-C31*$B$5:$B$12+B31*C31*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E31" s="55">
+        <f>SQRT(D31/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F31" s="56">
+        <f>(D31-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G31" s="67">
+        <f>IF(F31&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+      <c r="M31" s="21" t="inlineStr">
+        <is>
+          <t>最佳 Xm（SSE 最小）</t>
+        </is>
+      </c>
+      <c r="N31" s="55">
+        <f>INDEX(A20:A68,MATCH(MIN(D20:D68),D20:D68,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="44" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="B32" s="64" t="n">
+        <v>21.8927</v>
+      </c>
+      <c r="C32" s="65" t="n">
+        <v>0.84136</v>
+      </c>
+      <c r="D32" s="66">
+        <f>SUMPRODUCT((A32*B32*C32*$B$5:$B$12/((1-C32*$B$5:$B$12)*(1-C32*$B$5:$B$12+B32*C32*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E32" s="55">
+        <f>SQRT(D32/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F32" s="56">
+        <f>(D32-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G32" s="67">
+        <f>IF(F32&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+      <c r="M32" s="21" t="inlineStr">
+        <is>
+          <t>數據無法排除的 Xm：下限</t>
+        </is>
+      </c>
+      <c r="N32" s="63">
+        <f>_xlfn.MINIFS(A20:A68,F20:F68,"&lt;=3.84")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="44" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="B33" s="64" t="n">
+        <v>12.8113</v>
+      </c>
+      <c r="C33" s="65" t="n">
+        <v>0.83235</v>
+      </c>
+      <c r="D33" s="66">
+        <f>SUMPRODUCT((A33*B33*C33*$B$5:$B$12/((1-C33*$B$5:$B$12)*(1-C33*$B$5:$B$12+B33*C33*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E33" s="55">
+        <f>SQRT(D33/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F33" s="56">
+        <f>(D33-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G33" s="67">
+        <f>IF(F33&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+      <c r="M33" s="21" t="inlineStr">
+        <is>
+          <t>數據無法排除的 Xm：上限</t>
+        </is>
+      </c>
+      <c r="N33" s="63">
+        <f>_xlfn.MAXIFS(A20:A68,F20:F68,"&lt;=3.84")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="44" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="B34" s="64" t="n">
+        <v>9.1891</v>
+      </c>
+      <c r="C34" s="65" t="n">
+        <v>0.82367</v>
+      </c>
+      <c r="D34" s="66">
+        <f>SUMPRODUCT((A34*B34*C34*$B$5:$B$12/((1-C34*$B$5:$B$12)*(1-C34*$B$5:$B$12+B34*C34*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E34" s="55">
+        <f>SQRT(D34/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F34" s="56">
+        <f>(D34-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G34" s="67">
+        <f>IF(F34&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+      <c r="M34" s="21" t="inlineStr">
+        <is>
+          <t>上限 ÷ 下限</t>
+        </is>
+      </c>
+      <c r="N34" s="70">
+        <f>N33/N32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="44" t="n">
+        <v>0.0675</v>
+      </c>
+      <c r="B35" s="64" t="n">
+        <v>7.2395</v>
+      </c>
+      <c r="C35" s="65" t="n">
+        <v>0.81529</v>
+      </c>
+      <c r="D35" s="66">
+        <f>SUMPRODUCT((A35*B35*C35*$B$5:$B$12/((1-C35*$B$5:$B$12)*(1-C35*$B$5:$B$12+B35*C35*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E35" s="55">
+        <f>SQRT(D35/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F35" s="56">
+        <f>(D35-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G35" s="67">
+        <f>IF(F35&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+      <c r="M35" s="18" t="inlineStr">
+        <is>
+          <t>σ 的估計：烘箱法三重複 SD 約 0.2 %wb ≈ 0.0025 g/g，加上 aw 計 ±0.015 在高 aw 處約造成 0.004 g/g，合起來約 0.005。把 σ 改成 0.003 或 0.008，看可接受範圍怎麼變。上限若等於 0.15，表示碰到表格邊界，實際可能更高。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="44" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B36" s="64" t="n">
+        <v>6.0202</v>
+      </c>
+      <c r="C36" s="65" t="n">
+        <v>0.80721</v>
+      </c>
+      <c r="D36" s="66">
+        <f>SUMPRODUCT((A36*B36*C36*$B$5:$B$12/((1-C36*$B$5:$B$12)*(1-C36*$B$5:$B$12+B36*C36*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E36" s="55">
+        <f>SQRT(D36/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F36" s="56">
+        <f>(D36-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G36" s="67">
+        <f>IF(F36&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="44" t="n">
+        <v>0.0725</v>
+      </c>
+      <c r="B37" s="64" t="n">
+        <v>5.1848</v>
+      </c>
+      <c r="C37" s="65" t="n">
+        <v>0.79941</v>
+      </c>
+      <c r="D37" s="66">
+        <f>SUMPRODUCT((A37*B37*C37*$B$5:$B$12/((1-C37*$B$5:$B$12)*(1-C37*$B$5:$B$12+B37*C37*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E37" s="55">
+        <f>SQRT(D37/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F37" s="56">
+        <f>(D37-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G37" s="67">
+        <f>IF(F37&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="44" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="B38" s="64" t="n">
+        <v>4.5761</v>
+      </c>
+      <c r="C38" s="65" t="n">
+        <v>0.79187</v>
+      </c>
+      <c r="D38" s="66">
+        <f>SUMPRODUCT((A38*B38*C38*$B$5:$B$12/((1-C38*$B$5:$B$12)*(1-C38*$B$5:$B$12+B38*C38*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E38" s="55">
+        <f>SQRT(D38/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F38" s="56">
+        <f>(D38-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G38" s="67">
+        <f>IF(F38&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="44" t="n">
+        <v>0.0775</v>
+      </c>
+      <c r="B39" s="64" t="n">
+        <v>4.1124</v>
+      </c>
+      <c r="C39" s="65" t="n">
+        <v>0.78459</v>
+      </c>
+      <c r="D39" s="66">
+        <f>SUMPRODUCT((A39*B39*C39*$B$5:$B$12/((1-C39*$B$5:$B$12)*(1-C39*$B$5:$B$12+B39*C39*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E39" s="55">
+        <f>SQRT(D39/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F39" s="56">
+        <f>(D39-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G39" s="67">
+        <f>IF(F39&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="44" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="B40" s="64" t="n">
+        <v>3.7471</v>
+      </c>
+      <c r="C40" s="65" t="n">
+        <v>0.77756</v>
+      </c>
+      <c r="D40" s="66">
+        <f>SUMPRODUCT((A40*B40*C40*$B$5:$B$12/((1-C40*$B$5:$B$12)*(1-C40*$B$5:$B$12+B40*C40*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E40" s="55">
+        <f>SQRT(D40/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F40" s="56">
+        <f>(D40-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G40" s="67">
+        <f>IF(F40&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>⑤ 自己試：調整 GAB 參數（可用「規劃求解」）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="44" t="n">
+        <v>0.0825</v>
+      </c>
+      <c r="B41" s="64" t="n">
+        <v>3.4515</v>
+      </c>
+      <c r="C41" s="65" t="n">
+        <v>0.77075</v>
+      </c>
+      <c r="D41" s="66">
+        <f>SUMPRODUCT((A41*B41*C41*$B$5:$B$12/((1-C41*$B$5:$B$12)*(1-C41*$B$5:$B$12+B41*C41*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E41" s="55">
+        <f>SQRT(D41/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F41" s="56">
+        <f>(D41-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G41" s="67">
+        <f>IF(F41&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+      <c r="M41" s="21" t="inlineStr">
+        <is>
+          <t>Xm (g/g)</t>
+        </is>
+      </c>
+      <c r="N41" s="71" t="n">
+        <v>0.065</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="44" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="B42" s="64" t="n">
+        <v>3.2073</v>
+      </c>
+      <c r="C42" s="65" t="n">
+        <v>0.76417</v>
+      </c>
+      <c r="D42" s="66">
+        <f>SUMPRODUCT((A42*B42*C42*$B$5:$B$12/((1-C42*$B$5:$B$12)*(1-C42*$B$5:$B$12+B42*C42*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E42" s="55">
+        <f>SQRT(D42/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F42" s="56">
+        <f>(D42-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G42" s="67">
+        <f>IF(F42&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+      <c r="M42" s="21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N42" s="58" t="n">
+        <v>9.19</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="44" t="n">
+        <v>0.08749999999999999</v>
+      </c>
+      <c r="B43" s="64" t="n">
+        <v>3.0018</v>
+      </c>
+      <c r="C43" s="65" t="n">
+        <v>0.7578</v>
+      </c>
+      <c r="D43" s="66">
+        <f>SUMPRODUCT((A43*B43*C43*$B$5:$B$12/((1-C43*$B$5:$B$12)*(1-C43*$B$5:$B$12+B43*C43*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E43" s="55">
+        <f>SQRT(D43/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F43" s="56">
+        <f>(D43-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G43" s="67">
+        <f>IF(F43&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+      <c r="M43" s="21" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="N43" s="71" t="n">
+        <v>0.8237</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="44" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="B44" s="64" t="n">
+        <v>2.8265</v>
+      </c>
+      <c r="C44" s="65" t="n">
+        <v>0.75163</v>
+      </c>
+      <c r="D44" s="66">
+        <f>SUMPRODUCT((A44*B44*C44*$B$5:$B$12/((1-C44*$B$5:$B$12)*(1-C44*$B$5:$B$12+B44*C44*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E44" s="55">
+        <f>SQRT(D44/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F44" s="56">
+        <f>(D44-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G44" s="67">
+        <f>IF(F44&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+      <c r="M44" s="21" t="inlineStr">
+        <is>
+          <t>SSE（烘箱法）</t>
+        </is>
+      </c>
+      <c r="N44" s="66">
+        <f>SUMPRODUCT((N41*N42*N43*$B$5:$B$12/((1-N43*$B$5:$B$12)*(1-N43*$B$5:$B$12+N42*N43*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="44" t="n">
+        <v>0.0925</v>
+      </c>
+      <c r="B45" s="64" t="n">
+        <v>2.6749</v>
+      </c>
+      <c r="C45" s="65" t="n">
+        <v>0.74565</v>
+      </c>
+      <c r="D45" s="66">
+        <f>SUMPRODUCT((A45*B45*C45*$B$5:$B$12/((1-C45*$B$5:$B$12)*(1-C45*$B$5:$B$12+B45*C45*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E45" s="55">
+        <f>SQRT(D45/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F45" s="56">
+        <f>(D45-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G45" s="67">
+        <f>IF(F45&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+      <c r="M45" s="21" t="inlineStr">
+        <is>
+          <t>RMSE (g/g)</t>
+        </is>
+      </c>
+      <c r="N45" s="55">
+        <f>SQRT(N44/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="44" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="B46" s="64" t="n">
+        <v>2.5425</v>
+      </c>
+      <c r="C46" s="65" t="n">
+        <v>0.73986</v>
+      </c>
+      <c r="D46" s="66">
+        <f>SUMPRODUCT((A46*B46*C46*$B$5:$B$12/((1-C46*$B$5:$B$12)*(1-C46*$B$5:$B$12+B46*C46*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E46" s="55">
+        <f>SQRT(D46/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F46" s="56">
+        <f>(D46-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G46" s="67">
+        <f>IF(F46&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+      <c r="M46" s="21" t="inlineStr">
+        <is>
+          <t>Δ（和 ④ 的最小 SSE 比）</t>
+        </is>
+      </c>
+      <c r="N46" s="56">
+        <f>(N44-MIN(D20:D68))/N30^2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="44" t="n">
+        <v>0.0975</v>
+      </c>
+      <c r="B47" s="64" t="n">
+        <v>2.4258</v>
+      </c>
+      <c r="C47" s="65" t="n">
+        <v>0.73424</v>
+      </c>
+      <c r="D47" s="66">
+        <f>SUMPRODUCT((A47*B47*C47*$B$5:$B$12/((1-C47*$B$5:$B$12)*(1-C47*$B$5:$B$12+B47*C47*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E47" s="55">
+        <f>SQRT(D47/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F47" s="56">
+        <f>(D47-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G47" s="67">
+        <f>IF(F47&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+      <c r="M47" s="18" t="inlineStr">
+        <is>
+          <t>規劃求解（資料 → 規劃求解）：目標 N44 設為最小值；變數儲存格 N42:N43；限制 N42 ≥ 0.5、N43 ≥ 0.5、N43 ≤ 0.999。固定 Xm 解一次，就等於重算 ④ 的一列。沒有規劃求解也沒關係：直接改數字，看下方第一張圖的紅線和 Δ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="44" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B48" s="64" t="n">
+        <v>2.322</v>
+      </c>
+      <c r="C48" s="65" t="n">
+        <v>0.72879</v>
+      </c>
+      <c r="D48" s="66">
+        <f>SUMPRODUCT((A48*B48*C48*$B$5:$B$12/((1-C48*$B$5:$B$12)*(1-C48*$B$5:$B$12+B48*C48*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E48" s="55">
+        <f>SQRT(D48/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F48" s="56">
+        <f>(D48-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G48" s="67">
+        <f>IF(F48&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="44" t="n">
+        <v>0.1025</v>
+      </c>
+      <c r="B49" s="64" t="n">
+        <v>2.229</v>
+      </c>
+      <c r="C49" s="65" t="n">
+        <v>0.7235</v>
+      </c>
+      <c r="D49" s="66">
+        <f>SUMPRODUCT((A49*B49*C49*$B$5:$B$12/((1-C49*$B$5:$B$12)*(1-C49*$B$5:$B$12+B49*C49*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E49" s="55">
+        <f>SQRT(D49/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F49" s="56">
+        <f>(D49-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G49" s="67">
+        <f>IF(F49&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="44" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="B50" s="64" t="n">
+        <v>2.1451</v>
+      </c>
+      <c r="C50" s="65" t="n">
+        <v>0.71837</v>
+      </c>
+      <c r="D50" s="66">
+        <f>SUMPRODUCT((A50*B50*C50*$B$5:$B$12/((1-C50*$B$5:$B$12)*(1-C50*$B$5:$B$12+B50*C50*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E50" s="55">
+        <f>SQRT(D50/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F50" s="56">
+        <f>(D50-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G50" s="67">
+        <f>IF(F50&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="44" t="n">
+        <v>0.1075</v>
+      </c>
+      <c r="B51" s="64" t="n">
+        <v>2.0691</v>
+      </c>
+      <c r="C51" s="65" t="n">
+        <v>0.71339</v>
+      </c>
+      <c r="D51" s="66">
+        <f>SUMPRODUCT((A51*B51*C51*$B$5:$B$12/((1-C51*$B$5:$B$12)*(1-C51*$B$5:$B$12+B51*C51*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E51" s="55">
+        <f>SQRT(D51/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F51" s="56">
+        <f>(D51-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G51" s="67">
+        <f>IF(F51&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="44" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="B52" s="64" t="n">
+        <v>1.9998</v>
+      </c>
+      <c r="C52" s="65" t="n">
+        <v>0.7085399999999999</v>
+      </c>
+      <c r="D52" s="66">
+        <f>SUMPRODUCT((A52*B52*C52*$B$5:$B$12/((1-C52*$B$5:$B$12)*(1-C52*$B$5:$B$12+B52*C52*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E52" s="55">
+        <f>SQRT(D52/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F52" s="56">
+        <f>(D52-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G52" s="67">
+        <f>IF(F52&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>⑥ 這組數據真正能回答的：目標 aw 對應多少水分？</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="44" t="n">
+        <v>0.1125</v>
+      </c>
+      <c r="B53" s="64" t="n">
+        <v>1.9363</v>
+      </c>
+      <c r="C53" s="65" t="n">
+        <v>0.70383</v>
+      </c>
+      <c r="D53" s="66">
+        <f>SUMPRODUCT((A53*B53*C53*$B$5:$B$12/((1-C53*$B$5:$B$12)*(1-C53*$B$5:$B$12+B53*C53*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E53" s="55">
+        <f>SQRT(D53/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F53" s="56">
+        <f>(D53-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G53" s="67">
+        <f>IF(F53&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+      <c r="M53" s="21" t="inlineStr">
+        <is>
+          <t>目標 aw（多數黴菌下限附近）</t>
+        </is>
+      </c>
+      <c r="N53" s="58" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="44" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="B54" s="64" t="n">
+        <v>1.8779</v>
+      </c>
+      <c r="C54" s="65" t="n">
+        <v>0.69926</v>
+      </c>
+      <c r="D54" s="66">
+        <f>SUMPRODUCT((A54*B54*C54*$B$5:$B$12/((1-C54*$B$5:$B$12)*(1-C54*$B$5:$B$12+B54*C54*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E54" s="55">
+        <f>SQRT(D54/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F54" s="56">
+        <f>(D54-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G54" s="67">
+        <f>IF(F54&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+      <c r="M54" s="21" t="inlineStr">
+        <is>
+          <t>烘箱法水分 (%wb)，內插</t>
+        </is>
+      </c>
+      <c r="N54" s="62">
+        <f>C12+(N53-B12)*(C10-C12)/(B10-B12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="44" t="n">
+        <v>0.1175</v>
+      </c>
+      <c r="B55" s="64" t="n">
+        <v>1.824</v>
+      </c>
+      <c r="C55" s="65" t="n">
+        <v>0.69481</v>
+      </c>
+      <c r="D55" s="66">
+        <f>SUMPRODUCT((A55*B55*C55*$B$5:$B$12/((1-C55*$B$5:$B$12)*(1-C55*$B$5:$B$12+B55*C55*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E55" s="55">
+        <f>SQRT(D55/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F55" s="56">
+        <f>(D55-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G55" s="67">
+        <f>IF(F55&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+      <c r="M55" s="18" t="inlineStr">
+        <is>
+          <t>用 final（aw 0.558）與 1655（aw 0.628）兩點做線性內插。內插有數據撐腰，比外插出來的 Xm 可靠得多。換數據時，請改成目標 aw 兩側的兩列。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="44" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="B56" s="64" t="n">
+        <v>1.774</v>
+      </c>
+      <c r="C56" s="65" t="n">
+        <v>0.69047</v>
+      </c>
+      <c r="D56" s="66">
+        <f>SUMPRODUCT((A56*B56*C56*$B$5:$B$12/((1-C56*$B$5:$B$12)*(1-C56*$B$5:$B$12+B56*C56*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E56" s="55">
+        <f>SQRT(D56/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F56" s="56">
+        <f>(D56-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G56" s="67">
+        <f>IF(F56&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="44" t="n">
+        <v>0.1225</v>
+      </c>
+      <c r="B57" s="64" t="n">
+        <v>1.7275</v>
+      </c>
+      <c r="C57" s="65" t="n">
+        <v>0.68626</v>
+      </c>
+      <c r="D57" s="66">
+        <f>SUMPRODUCT((A57*B57*C57*$B$5:$B$12/((1-C57*$B$5:$B$12)*(1-C57*$B$5:$B$12+B57*C57*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E57" s="55">
+        <f>SQRT(D57/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F57" s="56">
+        <f>(D57-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G57" s="67">
+        <f>IF(F57&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="44" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="B58" s="64" t="n">
+        <v>1.6841</v>
+      </c>
+      <c r="C58" s="65" t="n">
+        <v>0.68215</v>
+      </c>
+      <c r="D58" s="66">
+        <f>SUMPRODUCT((A58*B58*C58*$B$5:$B$12/((1-C58*$B$5:$B$12)*(1-C58*$B$5:$B$12+B58*C58*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E58" s="55">
+        <f>SQRT(D58/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F58" s="56">
+        <f>(D58-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G58" s="67">
+        <f>IF(F58&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="44" t="n">
+        <v>0.1275</v>
+      </c>
+      <c r="B59" s="64" t="n">
+        <v>1.6436</v>
+      </c>
+      <c r="C59" s="65" t="n">
+        <v>0.67816</v>
+      </c>
+      <c r="D59" s="66">
+        <f>SUMPRODUCT((A59*B59*C59*$B$5:$B$12/((1-C59*$B$5:$B$12)*(1-C59*$B$5:$B$12+B59*C59*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E59" s="55">
+        <f>SQRT(D59/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F59" s="56">
+        <f>(D59-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G59" s="67">
+        <f>IF(F59&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>⑦ 對答案：用內建數據時，你的結果應該等於</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="44" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="B60" s="64" t="n">
+        <v>1.6055</v>
+      </c>
+      <c r="C60" s="65" t="n">
+        <v>0.67426</v>
+      </c>
+      <c r="D60" s="66">
+        <f>SUMPRODUCT((A60*B60*C60*$B$5:$B$12/((1-C60*$B$5:$B$12)*(1-C60*$B$5:$B$12+B60*C60*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E60" s="55">
+        <f>SQRT(D60/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F60" s="56">
+        <f>(D60-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G60" s="67">
+        <f>IF(F60&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+      <c r="M60" s="9" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="N60" s="9" t="inlineStr">
+        <is>
+          <t>本表的值</t>
+        </is>
+      </c>
+      <c r="O60" s="9" t="inlineStr">
+        <is>
+          <t>Colab 的值</t>
+        </is>
+      </c>
+      <c r="P60" s="9" t="inlineStr">
+        <is>
+          <t>一致？</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="44" t="n">
+        <v>0.1325</v>
+      </c>
+      <c r="B61" s="64" t="n">
+        <v>1.5697</v>
+      </c>
+      <c r="C61" s="65" t="n">
+        <v>0.6704599999999999</v>
+      </c>
+      <c r="D61" s="66">
+        <f>SUMPRODUCT((A61*B61*C61*$B$5:$B$12/((1-C61*$B$5:$B$12)*(1-C61*$B$5:$B$12+B61*C61*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E61" s="55">
+        <f>SQRT(D61/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F61" s="56">
+        <f>(D61-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G61" s="67">
+        <f>IF(F61&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+      <c r="M61" s="21" t="inlineStr">
+        <is>
+          <t>BET C（全部 8 點）</t>
+        </is>
+      </c>
+      <c r="N61" s="56">
+        <f>N10</f>
+        <v/>
+      </c>
+      <c r="O61" s="17" t="n">
+        <v>-1.46021176344256</v>
+      </c>
+      <c r="P61" s="67">
+        <f>IF(ABS(N61-O61)&lt;=0.000146022176344256,"✔ 一致","✘ 不一致")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="44" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="B62" s="64" t="n">
+        <v>1.5359</v>
+      </c>
+      <c r="C62" s="65" t="n">
+        <v>0.66676</v>
+      </c>
+      <c r="D62" s="66">
+        <f>SUMPRODUCT((A62*B62*C62*$B$5:$B$12/((1-C62*$B$5:$B$12)*(1-C62*$B$5:$B$12+B62*C62*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E62" s="55">
+        <f>SQRT(D62/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F62" s="56">
+        <f>(D62-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G62" s="67">
+        <f>IF(F62&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+      <c r="M62" s="21" t="inlineStr">
+        <is>
+          <t>BET Xm (g/g)</t>
+        </is>
+      </c>
+      <c r="N62" s="55">
+        <f>N11</f>
+        <v/>
+      </c>
+      <c r="O62" s="44" t="n">
+        <v>0.02673842251365445</v>
+      </c>
+      <c r="P62" s="67">
+        <f>IF(ABS(N62-O62)&lt;=2.6748422513654454e-06,"✔ 一致","✘ 不一致")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="44" t="n">
+        <v>0.1375</v>
+      </c>
+      <c r="B63" s="64" t="n">
+        <v>1.504</v>
+      </c>
+      <c r="C63" s="65" t="n">
+        <v>0.66315</v>
+      </c>
+      <c r="D63" s="66">
+        <f>SUMPRODUCT((A63*B63*C63*$B$5:$B$12/((1-C63*$B$5:$B$12)*(1-C63*$B$5:$B$12+B63*C63*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E63" s="55">
+        <f>SQRT(D63/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F63" s="56">
+        <f>(D63-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G63" s="67">
+        <f>IF(F63&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+      <c r="M63" s="21" t="inlineStr">
+        <is>
+          <t>GAB 二次式 Xm (g/g)</t>
+        </is>
+      </c>
+      <c r="N63" s="55">
+        <f>N22</f>
+        <v/>
+      </c>
+      <c r="O63" s="44" t="n">
+        <v>0.04975071102997377</v>
+      </c>
+      <c r="P63" s="67">
+        <f>IF(ABS(N63-O63)&lt;=4.976071102997377e-06,"✔ 一致","✘ 不一致")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="44" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="B64" s="64" t="n">
+        <v>1.4739</v>
+      </c>
+      <c r="C64" s="65" t="n">
+        <v>0.65963</v>
+      </c>
+      <c r="D64" s="66">
+        <f>SUMPRODUCT((A64*B64*C64*$B$5:$B$12/((1-C64*$B$5:$B$12)*(1-C64*$B$5:$B$12+B64*C64*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E64" s="55">
+        <f>SQRT(D64/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F64" s="56">
+        <f>(D64-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G64" s="67">
+        <f>IF(F64&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+      <c r="M64" s="21" t="inlineStr">
+        <is>
+          <t>GAB 二次式 C</t>
+        </is>
+      </c>
+      <c r="N64" s="56">
+        <f>N23</f>
+        <v/>
+      </c>
+      <c r="O64" s="17" t="n">
+        <v>-9.267410630247591</v>
+      </c>
+      <c r="P64" s="67">
+        <f>IF(ABS(N64-O64)&lt;=0.0009267420630247592,"✔ 一致","✘ 不一致")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="44" t="n">
+        <v>0.1425</v>
+      </c>
+      <c r="B65" s="64" t="n">
+        <v>1.4452</v>
+      </c>
+      <c r="C65" s="65" t="n">
+        <v>0.6562</v>
+      </c>
+      <c r="D65" s="66">
+        <f>SUMPRODUCT((A65*B65*C65*$B$5:$B$12/((1-C65*$B$5:$B$12)*(1-C65*$B$5:$B$12+B65*C65*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E65" s="55">
+        <f>SQRT(D65/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F65" s="56">
+        <f>(D65-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G65" s="67">
+        <f>IF(F65&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+      <c r="M65" s="21" t="inlineStr">
+        <is>
+          <t>Xm 可接受下限（σ = 0.005）</t>
+        </is>
+      </c>
+      <c r="N65" s="55">
+        <f>N32</f>
+        <v/>
+      </c>
+      <c r="O65" s="44" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="P65" s="67">
+        <f>IF(ABS(N65-O65)&lt;=5.501e-06,"✔ 一致","✘ 不一致")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="44" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="B66" s="64" t="n">
+        <v>1.4181</v>
+      </c>
+      <c r="C66" s="65" t="n">
+        <v>0.65284</v>
+      </c>
+      <c r="D66" s="66">
+        <f>SUMPRODUCT((A66*B66*C66*$B$5:$B$12/((1-C66*$B$5:$B$12)*(1-C66*$B$5:$B$12+B66*C66*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E66" s="55">
+        <f>SQRT(D66/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F66" s="56">
+        <f>(D66-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G66" s="67">
+        <f>IF(F66&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+      <c r="M66" s="21" t="inlineStr">
+        <is>
+          <t>Xm 可接受上限（σ = 0.005）</t>
+        </is>
+      </c>
+      <c r="N66" s="55">
+        <f>N33</f>
+        <v/>
+      </c>
+      <c r="O66" s="44" t="n">
+        <v>0.1125</v>
+      </c>
+      <c r="P66" s="67">
+        <f>IF(ABS(N66-O66)&lt;=1.1251000000000001e-05,"✔ 一致","✘ 不一致")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="44" t="n">
+        <v>0.1475</v>
+      </c>
+      <c r="B67" s="64" t="n">
+        <v>1.3922</v>
+      </c>
+      <c r="C67" s="65" t="n">
+        <v>0.64957</v>
+      </c>
+      <c r="D67" s="66">
+        <f>SUMPRODUCT((A67*B67*C67*$B$5:$B$12/((1-C67*$B$5:$B$12)*(1-C67*$B$5:$B$12+B67*C67*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E67" s="55">
+        <f>SQRT(D67/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F67" s="56">
+        <f>(D67-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G67" s="67">
+        <f>IF(F67&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+      <c r="M67" s="21" t="inlineStr">
+        <is>
+          <t>aw 0.6 對應水分 (%wb)</t>
+        </is>
+      </c>
+      <c r="N67" s="56">
+        <f>N54</f>
+        <v/>
+      </c>
+      <c r="O67" s="17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="P67" s="67">
+        <f>IF(ABS(N67-O67)&lt;=0.001050001,"✔ 一致","✘ 不一致")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="44" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="B68" s="64" t="n">
+        <v>1.3675</v>
+      </c>
+      <c r="C68" s="65" t="n">
+        <v>0.64637</v>
+      </c>
+      <c r="D68" s="66">
+        <f>SUMPRODUCT((A68*B68*C68*$B$5:$B$12/((1-C68*$B$5:$B$12)*(1-C68*$B$5:$B$12+B68*C68*$B$5:$B$12))-$E$5:$E$12)^2)</f>
+        <v/>
+      </c>
+      <c r="E68" s="55">
+        <f>SQRT(D68/COUNT($B$5:$B$12))</f>
+        <v/>
+      </c>
+      <c r="F68" s="56">
+        <f>(D68-MIN($D$20:$D$68))/$N$30^2</f>
+        <v/>
+      </c>
+      <c r="G68" s="67">
+        <f>IF(F68&lt;=3.84,"數據分不出來","數據排除")</f>
+        <v/>
+      </c>
+      <c r="M68" s="18" t="inlineStr">
+        <is>
+          <t>「Colab 的值」來自 NB02 第 7 節；σ 或 ① 的數據改過之後，這一欄就不再適用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69"/>
   </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="M13:P15"/>
+    <mergeCell ref="A16:K18"/>
+    <mergeCell ref="M47:P50"/>
+    <mergeCell ref="M25:P27"/>
+    <mergeCell ref="M68:P69"/>
+    <mergeCell ref="A13:K13"/>
+    <mergeCell ref="M35:P38"/>
+    <mergeCell ref="M55:P57"/>
+    <mergeCell ref="A2:P2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="F20:G68">
+    <cfRule type="cellIs" priority="1" operator="lessThanOrEqual" dxfId="2">
+      <formula>3.84</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="N4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"烘箱法,FD-660"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>